--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35927F40-13FA-414D-9A66-C4DFBEC34484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8480C6A9-F3DE-4B24-BEBB-4D0A8F9431AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34981AB-89B6-4F33-9D6B-F21C9FEDC8F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C35E2C2-CD2C-470A-93D4-8B9C0C2515C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t>MARCOS</t>
-  </si>
-  <si>
-    <t>43752263</t>
   </si>
   <si>
     <t>43407464</t>
@@ -915,7 +912,7 @@
   <sheetData>
     <row r="1" spans="1:41" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>37</v>
@@ -924,10 +921,10 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>39</v>
@@ -936,7 +933,7 @@
         <v>40</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>41</v>
@@ -993,49 +990,49 @@
         <v>44</v>
       </c>
       <c r="AA1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AD1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AG1" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="AH1" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AI1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="AO1" s="9" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
@@ -1049,19 +1046,19 @@
         <v>4991589</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G2" s="6">
         <v>46117</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I2" s="3">
         <v>120</v>
@@ -1129,16 +1126,16 @@
         <v>50</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G3" s="6">
         <v>46147</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I3" s="3">
         <v>72</v>
@@ -1202,20 +1199,20 @@
       <c r="C4" s="5">
         <v>4991874</v>
       </c>
-      <c r="D4" s="5">
-        <v>43627383</v>
+      <c r="D4" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G4" s="6">
         <v>46147</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I4" s="3">
         <v>48</v>
@@ -1275,20 +1272,20 @@
       <c r="C5" s="5">
         <v>4991815</v>
       </c>
-      <c r="D5" s="5">
-        <v>43407464</v>
+      <c r="D5" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G5" s="6">
         <v>46147</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I5" s="3">
         <v>36</v>
@@ -1352,16 +1349,16 @@
         <v>43409454</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="6">
         <v>46117</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I6" s="3">
         <v>72</v>
@@ -1425,16 +1422,16 @@
         <v>43632407</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" s="6">
         <v>46142</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I7" s="3">
         <v>120</v>
@@ -1500,16 +1497,16 @@
         <v>43559375</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="6">
         <v>46142</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I8" s="3">
         <v>72</v>
@@ -1575,16 +1572,16 @@
         <v>43286101</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9" s="6">
         <v>46172</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I9" s="3">
         <v>144</v>
@@ -1646,16 +1643,16 @@
         <v>43389459</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" s="6">
         <v>46132</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I10" s="3">
         <v>36</v>
@@ -1719,16 +1716,16 @@
         <v>43306412</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G11" s="6">
         <v>46132</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I11" s="3">
         <v>24</v>
@@ -1794,16 +1791,16 @@
         <v>43336749</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="G12" s="6">
         <v>46132</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I12" s="3">
         <v>12</v>
@@ -1867,16 +1864,16 @@
         <v>43213474</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="G13" s="6">
         <v>46132</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I13" s="3">
         <v>48</v>
@@ -1940,16 +1937,16 @@
         <v>43649393</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G14" s="6">
         <v>46132</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I14" s="3">
         <v>36</v>
@@ -2015,16 +2012,16 @@
         <v>43632407</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="6">
         <v>46103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I15" s="3">
         <v>108</v>
@@ -2088,16 +2085,16 @@
         <v>43299316</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G16" s="6">
         <v>46104</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I16" s="3">
         <v>48</v>
@@ -2161,16 +2158,16 @@
         <v>43418328</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17" s="6">
         <v>46103</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I17" s="3">
         <v>108</v>
@@ -2234,16 +2231,16 @@
         <v>43697386</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="6">
         <v>46104</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I18" s="3">
         <v>60</v>
@@ -2307,16 +2304,16 @@
         <v>43242437</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G19" s="6">
         <v>46103</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I19" s="3">
         <v>48</v>
@@ -2380,16 +2377,16 @@
         <v>43358451</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G20" s="6">
         <v>46103</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I20" s="3">
         <v>48</v>
@@ -2453,16 +2450,16 @@
         <v>54111405</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" s="6">
         <v>46172</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I21" s="3">
         <v>144</v>
@@ -2526,16 +2523,16 @@
         <v>43758365</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" s="6">
         <v>46142</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I22" s="3">
         <v>60</v>
@@ -2592,19 +2589,19 @@
         <v>791970</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="6">
         <v>46196</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I23" s="3">
         <v>120</v>
@@ -2661,19 +2658,19 @@
         <v>793473</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="6">
         <v>46076</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I24" s="3">
         <v>240</v>
@@ -2709,7 +2706,7 @@
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
       <c r="AN24" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AO24" s="4"/>
     </row>
@@ -2724,19 +2721,19 @@
         <v>1251823</v>
       </c>
       <c r="D25" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G25" s="6">
         <v>46045</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I25" s="3">
         <v>96</v>
@@ -2771,7 +2768,7 @@
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AN25" s="4"/>
       <c r="AO25" s="4"/>
@@ -2790,16 +2787,16 @@
         <v>43341472</v>
       </c>
       <c r="E26" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="G26" s="6">
         <v>46132</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I26" s="3">
         <v>60</v>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E42B30-C72D-4A1D-AFC2-ABA1DDB74277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB31CFD3-0614-4486-A0EA-23179CBC9FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB31CFD3-0614-4486-A0EA-23179CBC9FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0F6AA1-1F4C-4A09-9FF4-E0A0BA67588A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$Z$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$Z$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -226,9 +226,6 @@
   </si>
   <si>
     <t>ATMOS</t>
-  </si>
-  <si>
-    <t>FLUTUA 2</t>
   </si>
   <si>
     <t>ACQUA</t>
@@ -890,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AO26"/>
+  <dimension ref="A1:AO25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
@@ -912,7 +909,7 @@
   <sheetData>
     <row r="1" spans="1:41" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>37</v>
@@ -921,10 +918,10 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>39</v>
@@ -933,7 +930,7 @@
         <v>40</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>41</v>
@@ -990,49 +987,49 @@
         <v>44</v>
       </c>
       <c r="AA1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AD1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="9" t="s">
-        <v>83</v>
-      </c>
       <c r="AH1" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AI1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="AO1" s="9" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
@@ -1058,7 +1055,7 @@
         <v>46117</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I2" s="3">
         <v>120</v>
@@ -1135,7 +1132,7 @@
         <v>46147</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I3" s="3">
         <v>72</v>
@@ -1212,7 +1209,7 @@
         <v>46147</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I4" s="3">
         <v>48</v>
@@ -1285,7 +1282,7 @@
         <v>46147</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I5" s="3">
         <v>36</v>
@@ -1358,7 +1355,7 @@
         <v>46117</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I6" s="3">
         <v>72</v>
@@ -1431,7 +1428,7 @@
         <v>46142</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I7" s="3">
         <v>120</v>
@@ -1506,7 +1503,7 @@
         <v>46142</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I8" s="3">
         <v>72</v>
@@ -1581,7 +1578,7 @@
         <v>46172</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I9" s="3">
         <v>144</v>
@@ -1631,57 +1628,59 @@
     </row>
     <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5">
-        <v>13185976</v>
+        <v>13185987</v>
       </c>
       <c r="C10" s="5">
-        <v>5245127</v>
+        <v>7283002</v>
       </c>
       <c r="D10" s="5">
-        <v>43389459</v>
+        <v>43306412</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G10" s="6">
         <v>46132</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I10" s="3">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
+      <c r="L10" s="4">
+        <v>1</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4">
+        <v>2</v>
+      </c>
+      <c r="O10" s="4">
+        <v>2</v>
+      </c>
+      <c r="P10" s="4">
+        <v>2</v>
+      </c>
       <c r="Q10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" s="4">
         <v>2</v>
       </c>
-      <c r="S10" s="4">
-        <v>3</v>
-      </c>
-      <c r="T10" s="4">
-        <v>3</v>
-      </c>
-      <c r="U10" s="4">
-        <v>2</v>
-      </c>
-      <c r="V10" s="4">
-        <v>1</v>
-      </c>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
@@ -1704,59 +1703,57 @@
     </row>
     <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5">
-        <v>13185987</v>
+        <v>13185986</v>
       </c>
       <c r="C11" s="5">
-        <v>7283002</v>
+        <v>7283001</v>
       </c>
       <c r="D11" s="5">
-        <v>43306412</v>
+        <v>43336749</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="G11" s="6">
         <v>46132</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I11" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="4">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4">
-        <v>1</v>
-      </c>
-      <c r="N11" s="4">
-        <v>2</v>
-      </c>
-      <c r="O11" s="4">
-        <v>2</v>
-      </c>
-      <c r="P11" s="4">
-        <v>2</v>
-      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
       <c r="Q11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" s="4">
-        <v>2</v>
-      </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="S11" s="4">
+        <v>3</v>
+      </c>
+      <c r="T11" s="4">
+        <v>2</v>
+      </c>
+      <c r="U11" s="4">
+        <v>2</v>
+      </c>
+      <c r="V11" s="4">
+        <v>1</v>
+      </c>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
@@ -1779,57 +1776,57 @@
     </row>
     <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="5">
-        <v>13185986</v>
+        <v>13185988</v>
       </c>
       <c r="C12" s="5">
-        <v>7283001</v>
+        <v>7283003</v>
       </c>
       <c r="D12" s="5">
-        <v>43336749</v>
+        <v>43213474</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" s="6">
         <v>46132</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I12" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4">
+        <v>2</v>
+      </c>
+      <c r="O12" s="4">
+        <v>3</v>
+      </c>
+      <c r="P12" s="4">
+        <v>3</v>
+      </c>
       <c r="Q12" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" s="4">
-        <v>3</v>
-      </c>
-      <c r="S12" s="4">
-        <v>3</v>
-      </c>
-      <c r="T12" s="4">
-        <v>2</v>
-      </c>
-      <c r="U12" s="4">
-        <v>2</v>
-      </c>
-      <c r="V12" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
@@ -1852,35 +1849,37 @@
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="5">
-        <v>13185988</v>
+        <v>13172698</v>
       </c>
       <c r="C13" s="5">
-        <v>7283003</v>
+        <v>7268502</v>
       </c>
       <c r="D13" s="5">
-        <v>43213474</v>
+        <v>43649393</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G13" s="6">
         <v>46132</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I13" s="3">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+      <c r="L13" s="4">
+        <v>1</v>
+      </c>
       <c r="M13" s="4">
         <v>1</v>
       </c>
@@ -1888,16 +1887,16 @@
         <v>2</v>
       </c>
       <c r="O13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="4">
         <v>2</v>
       </c>
       <c r="R13" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" s="4"/>
       <c r="T13" s="4"/>
@@ -1925,58 +1924,56 @@
     </row>
     <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="5">
-        <v>13172698</v>
+        <v>13167977</v>
       </c>
       <c r="C14" s="5">
-        <v>7268502</v>
+        <v>5235628</v>
       </c>
       <c r="D14" s="5">
-        <v>43649393</v>
+        <v>43632407</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G14" s="6">
-        <v>46132</v>
+        <v>46103</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I14" s="3">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="4">
-        <v>1</v>
-      </c>
-      <c r="M14" s="4">
-        <v>1</v>
-      </c>
-      <c r="N14" s="4">
-        <v>2</v>
-      </c>
-      <c r="O14" s="4">
-        <v>2</v>
-      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
       <c r="P14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="4">
         <v>2</v>
       </c>
       <c r="R14" s="4">
-        <v>2</v>
-      </c>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="S14" s="4">
+        <v>3</v>
+      </c>
+      <c r="T14" s="4">
+        <v>2</v>
+      </c>
+      <c r="U14" s="4">
+        <v>1</v>
+      </c>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
@@ -2000,31 +1997,31 @@
     </row>
     <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="5">
-        <v>13167977</v>
+        <v>13159168</v>
       </c>
       <c r="C15" s="5">
-        <v>5235628</v>
+        <v>7254752</v>
       </c>
       <c r="D15" s="5">
-        <v>43632407</v>
+        <v>43299316</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G15" s="6">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>106</v>
       </c>
       <c r="I15" s="3">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -2032,11 +2029,9 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="4">
-        <v>1</v>
-      </c>
+      <c r="P15" s="4"/>
       <c r="Q15" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" s="4">
         <v>3</v>
@@ -2048,9 +2043,11 @@
         <v>2</v>
       </c>
       <c r="U15" s="4">
-        <v>1</v>
-      </c>
-      <c r="V15" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="V15" s="4">
+        <v>1</v>
+      </c>
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
@@ -2073,31 +2070,31 @@
     </row>
     <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>13159168</v>
+        <v>13167968</v>
       </c>
       <c r="C16" s="5">
-        <v>7254752</v>
+        <v>7263895</v>
       </c>
       <c r="D16" s="5">
-        <v>43299316</v>
+        <v>43418328</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>54</v>
       </c>
       <c r="G16" s="6">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I16" s="3">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -2105,9 +2102,11 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <v>1</v>
+      </c>
       <c r="Q16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" s="4">
         <v>3</v>
@@ -2119,11 +2118,9 @@
         <v>2</v>
       </c>
       <c r="U16" s="4">
-        <v>2</v>
-      </c>
-      <c r="V16" s="4">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V16" s="4"/>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2146,31 +2143,31 @@
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>13167968</v>
+        <v>13159121</v>
       </c>
       <c r="C17" s="5">
-        <v>7263895</v>
+        <v>5226145</v>
       </c>
       <c r="D17" s="5">
-        <v>43418328</v>
+        <v>43697386</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G17" s="6">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="3">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -2178,25 +2175,25 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="4">
-        <v>1</v>
-      </c>
+      <c r="P17" s="4"/>
       <c r="Q17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S17" s="4">
         <v>3</v>
       </c>
       <c r="T17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" s="4">
-        <v>1</v>
-      </c>
-      <c r="V17" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="V17" s="4">
+        <v>1</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -2219,31 +2216,31 @@
     </row>
     <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="5">
-        <v>13159121</v>
+        <v>13167974</v>
       </c>
       <c r="C18" s="5">
-        <v>5226145</v>
+        <v>5235626</v>
       </c>
       <c r="D18" s="5">
-        <v>43697386</v>
+        <v>43242437</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G18" s="6">
-        <v>46104</v>
+        <v>46103</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I18" s="3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -2252,28 +2249,28 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
-      <c r="Q18" s="4">
-        <v>1</v>
-      </c>
-      <c r="R18" s="4">
-        <v>2</v>
-      </c>
-      <c r="S18" s="4">
-        <v>3</v>
-      </c>
-      <c r="T18" s="4">
-        <v>3</v>
-      </c>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
       <c r="U18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18" s="4">
-        <v>1</v>
-      </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="W18" s="4">
+        <v>3</v>
+      </c>
+      <c r="X18" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>1</v>
+      </c>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2292,28 +2289,28 @@
     </row>
     <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="5">
-        <v>13167974</v>
+        <v>13167975</v>
       </c>
       <c r="C19" s="5">
-        <v>5235626</v>
+        <v>5235627</v>
       </c>
       <c r="D19" s="5">
-        <v>43242437</v>
+        <v>43358451</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G19" s="6">
         <v>46103</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I19" s="3">
         <v>48</v>
@@ -2365,31 +2362,31 @@
     </row>
     <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="5">
-        <v>13167975</v>
+        <v>13167976</v>
       </c>
       <c r="C20" s="5">
-        <v>5235627</v>
+        <v>5060906</v>
       </c>
       <c r="D20" s="5">
-        <v>43358451</v>
+        <v>54111405</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" s="6">
-        <v>46103</v>
+        <v>46172</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I20" s="3">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -2402,30 +2399,30 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="4">
-        <v>1</v>
-      </c>
-      <c r="V20" s="4">
-        <v>2</v>
-      </c>
-      <c r="W20" s="4">
-        <v>3</v>
-      </c>
-      <c r="X20" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="4"/>
-      <c r="AB20" s="4"/>
-      <c r="AC20" s="4"/>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
-      <c r="AF20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="4">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="4">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="4">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="4">
+        <v>2</v>
+      </c>
+      <c r="AF20" s="4">
+        <v>1</v>
+      </c>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="4"/>
@@ -2438,31 +2435,31 @@
     </row>
     <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="5">
-        <v>13167976</v>
+        <v>13167979</v>
       </c>
       <c r="C21" s="5">
-        <v>5060906</v>
+        <v>6874170</v>
       </c>
       <c r="D21" s="5">
-        <v>54111405</v>
+        <v>43758365</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>94</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G21" s="6">
-        <v>46172</v>
+        <v>46142</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I21" s="3">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -2474,31 +2471,27 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
+      <c r="T21" s="4">
+        <v>1</v>
+      </c>
+      <c r="U21" s="4">
+        <v>2</v>
+      </c>
+      <c r="V21" s="4">
+        <v>2</v>
+      </c>
+      <c r="W21" s="4">
+        <v>1</v>
+      </c>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
-      <c r="AA21" s="4">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="4">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="4">
-        <v>3</v>
-      </c>
-      <c r="AD21" s="4">
-        <v>3</v>
-      </c>
-      <c r="AE21" s="4">
-        <v>2</v>
-      </c>
-      <c r="AF21" s="4">
-        <v>1</v>
-      </c>
+      <c r="AA21" s="4"/>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4"/>
+      <c r="AF21" s="4"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
       <c r="AI21" s="4"/>
@@ -2511,31 +2504,31 @@
     </row>
     <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="5">
-        <v>13167979</v>
+        <v>13167978</v>
       </c>
       <c r="C22" s="5">
-        <v>6874170</v>
-      </c>
-      <c r="D22" s="5">
-        <v>43758365</v>
+        <v>791970</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G22" s="6">
-        <v>46142</v>
+        <v>46196</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I22" s="3">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
@@ -2547,18 +2540,10 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
-      <c r="T22" s="4">
-        <v>1</v>
-      </c>
-      <c r="U22" s="4">
-        <v>2</v>
-      </c>
-      <c r="V22" s="4">
-        <v>2</v>
-      </c>
-      <c r="W22" s="4">
-        <v>1</v>
-      </c>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
@@ -2570,41 +2555,49 @@
       <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
-      <c r="AI22" s="4"/>
-      <c r="AJ22" s="4"/>
-      <c r="AK22" s="4"/>
-      <c r="AL22" s="4"/>
+      <c r="AI22" s="4">
+        <v>1</v>
+      </c>
+      <c r="AJ22" s="4">
+        <v>2</v>
+      </c>
+      <c r="AK22" s="4">
+        <v>2</v>
+      </c>
+      <c r="AL22" s="4">
+        <v>1</v>
+      </c>
       <c r="AM22" s="4"/>
       <c r="AN22" s="4"/>
       <c r="AO22" s="4"/>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="5">
-        <v>13167978</v>
+        <v>13167973</v>
       </c>
       <c r="C23" s="5">
-        <v>791970</v>
+        <v>793473</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G23" s="6">
-        <v>46196</v>
+        <v>46076</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I23" s="3">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
@@ -2631,49 +2624,43 @@
       <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
-      <c r="AI23" s="4">
-        <v>1</v>
-      </c>
-      <c r="AJ23" s="4">
-        <v>2</v>
-      </c>
-      <c r="AK23" s="4">
-        <v>2</v>
-      </c>
-      <c r="AL23" s="4">
-        <v>1</v>
-      </c>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="4"/>
+      <c r="AN23" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="AO23" s="4"/>
     </row>
     <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="5">
-        <v>13167973</v>
+        <v>13167972</v>
       </c>
       <c r="C24" s="5">
-        <v>793473</v>
+        <v>1251823</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G24" s="6">
-        <v>46076</v>
+        <v>46045</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I24" s="3">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
@@ -2704,39 +2691,39 @@
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
-      <c r="AM24" s="4"/>
-      <c r="AN24" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="AM24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN24" s="4"/>
       <c r="AO24" s="4"/>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="5">
-        <v>13167972</v>
+        <v>13172698</v>
       </c>
       <c r="C25" s="5">
-        <v>1251823</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>100</v>
+        <v>7268502</v>
+      </c>
+      <c r="D25" s="5">
+        <v>43341472</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>101</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="G25" s="6">
-        <v>46045</v>
+        <v>46132</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I25" s="3">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
@@ -2750,11 +2737,21 @@
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4"/>
+      <c r="V25" s="4">
+        <v>2</v>
+      </c>
+      <c r="W25" s="4">
+        <v>2</v>
+      </c>
+      <c r="X25" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y25" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z25" s="4">
+        <v>2</v>
+      </c>
       <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
@@ -2767,91 +2764,18 @@
       <c r="AJ25" s="4"/>
       <c r="AK25" s="4"/>
       <c r="AL25" s="4"/>
-      <c r="AM25" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="AM25" s="4"/>
       <c r="AN25" s="4"/>
       <c r="AO25" s="4"/>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5">
-        <v>13172698</v>
-      </c>
-      <c r="C26" s="5">
-        <v>7268502</v>
-      </c>
-      <c r="D26" s="5">
-        <v>43341472</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" s="6">
-        <v>46132</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I26" s="3">
-        <v>60</v>
-      </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4">
-        <v>2</v>
-      </c>
-      <c r="W26" s="4">
-        <v>2</v>
-      </c>
-      <c r="X26" s="4">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="4">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="4">
-        <v>2</v>
-      </c>
-      <c r="AA26" s="4"/>
-      <c r="AB26" s="4"/>
-      <c r="AC26" s="4"/>
-      <c r="AD26" s="4"/>
-      <c r="AE26" s="4"/>
-      <c r="AF26" s="4"/>
-      <c r="AG26" s="4"/>
-      <c r="AH26" s="4"/>
-      <c r="AI26" s="4"/>
-      <c r="AJ26" s="4"/>
-      <c r="AK26" s="4"/>
-      <c r="AL26" s="4"/>
-      <c r="AM26" s="4"/>
-      <c r="AN26" s="4"/>
-      <c r="AO26" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:Z20" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
+  <autoFilter ref="B1:Z19" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B26">
-    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  <conditionalFormatting sqref="B2:B25">
+    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36532736-C3BE-4E5B-A3CC-C7FFCAAF5527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D96140-4FFA-46DB-A91D-08EC6066264B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$Z$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$AA$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -358,6 +358,21 @@
   </si>
   <si>
     <t>NÃO</t>
+  </si>
+  <si>
+    <t>FILIAL</t>
+  </si>
+  <si>
+    <t>VULTZ</t>
+  </si>
+  <si>
+    <t>AZABA</t>
+  </si>
+  <si>
+    <t>VULCA</t>
+  </si>
+  <si>
+    <t>VDIST</t>
   </si>
 </sst>
 </file>
@@ -884,27 +899,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AO25"/>
+  <dimension ref="A1:AP25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="21" width="3.42578125" customWidth="1"/>
-    <col min="22" max="22" width="4.42578125" customWidth="1"/>
-    <col min="23" max="23" width="5.140625" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" customWidth="1"/>
-    <col min="26" max="26" width="4.5703125" customWidth="1"/>
-    <col min="27" max="41" width="6.140625" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="3.42578125" customWidth="1"/>
+    <col min="23" max="23" width="4.42578125" customWidth="1"/>
+    <col min="24" max="24" width="5.140625" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" customWidth="1"/>
+    <col min="27" max="27" width="4.5703125" customWidth="1"/>
+    <col min="28" max="42" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>102</v>
       </c>
@@ -915,121 +930,124 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="9">
+      <c r="K1" s="9">
         <v>28</v>
       </c>
-      <c r="K1" s="9">
+      <c r="L1" s="9">
         <v>29</v>
       </c>
-      <c r="L1" s="9">
+      <c r="M1" s="9">
         <v>30</v>
       </c>
-      <c r="M1" s="9">
+      <c r="N1" s="9">
         <v>31</v>
       </c>
-      <c r="N1" s="9">
+      <c r="O1" s="9">
         <v>32</v>
       </c>
-      <c r="O1" s="9">
+      <c r="P1" s="9">
         <v>33</v>
       </c>
-      <c r="P1" s="9">
+      <c r="Q1" s="9">
         <v>34</v>
       </c>
-      <c r="Q1" s="9">
+      <c r="R1" s="9">
         <v>35</v>
       </c>
-      <c r="R1" s="9">
+      <c r="S1" s="9">
         <v>36</v>
       </c>
-      <c r="S1" s="9">
+      <c r="T1" s="9">
         <v>37</v>
       </c>
-      <c r="T1" s="9">
+      <c r="U1" s="9">
         <v>38</v>
       </c>
-      <c r="U1" s="9">
+      <c r="V1" s="9">
         <v>39</v>
       </c>
-      <c r="V1" s="10">
+      <c r="W1" s="10">
         <v>40</v>
       </c>
-      <c r="W1" s="9">
+      <c r="X1" s="9">
         <v>41</v>
       </c>
-      <c r="X1" s="9">
+      <c r="Y1" s="9">
         <v>42</v>
       </c>
-      <c r="Y1" s="9">
+      <c r="Z1" s="9">
         <v>43</v>
       </c>
-      <c r="Z1" s="9">
+      <c r="AA1" s="9">
         <v>44</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AB1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AD1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AI1" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AJ1" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AP1" s="9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1040,24 +1058,26 @@
         <v>4991589</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="6">
+      <c r="H2" s="6">
         <v>46117</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I2" s="3">
+      <c r="J2" s="3">
         <v>120</v>
       </c>
-      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -1066,14 +1086,12 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="4">
-        <v>1</v>
-      </c>
+      <c r="S2" s="4"/>
       <c r="T2" s="4">
         <v>1</v>
       </c>
       <c r="U2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" s="4">
         <v>2</v>
@@ -1085,12 +1103,14 @@
         <v>2</v>
       </c>
       <c r="Y2" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2" s="4">
         <v>1</v>
       </c>
-      <c r="AA2" s="4"/>
+      <c r="AA2" s="4">
+        <v>1</v>
+      </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
@@ -1105,8 +1125,9 @@
       <c r="AM2" s="4"/>
       <c r="AN2" s="4"/>
       <c r="AO2" s="4"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP2" s="4"/>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1117,24 +1138,26 @@
         <v>4991830</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="6">
+      <c r="H3" s="6">
         <v>46147</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I3" s="3">
+      <c r="J3" s="3">
         <v>72</v>
       </c>
-      <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -1143,14 +1166,12 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="4">
-        <v>1</v>
-      </c>
+      <c r="S3" s="4"/>
       <c r="T3" s="4">
         <v>1</v>
       </c>
       <c r="U3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V3" s="4">
         <v>2</v>
@@ -1162,12 +1183,14 @@
         <v>2</v>
       </c>
       <c r="Y3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" s="4">
         <v>1</v>
       </c>
-      <c r="AA3" s="4"/>
+      <c r="AA3" s="4">
+        <v>1</v>
+      </c>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
       <c r="AD3" s="4"/>
@@ -1182,8 +1205,9 @@
       <c r="AM3" s="4"/>
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP3" s="4"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1194,49 +1218,51 @@
         <v>4991874</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>46147</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <v>48</v>
       </c>
-      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q4" s="4"/>
       <c r="R4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4" s="4">
         <v>3</v>
       </c>
       <c r="U4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" s="4">
-        <v>1</v>
-      </c>
-      <c r="W4" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="W4" s="4">
+        <v>1</v>
+      </c>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
@@ -1255,8 +1281,9 @@
       <c r="AM4" s="4"/>
       <c r="AN4" s="4"/>
       <c r="AO4" s="4"/>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP4" s="4"/>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1267,24 +1294,26 @@
         <v>4991815</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <v>46147</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>36</v>
       </c>
-      <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1294,25 +1323,25 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4">
-        <v>1</v>
-      </c>
+      <c r="T5" s="4"/>
       <c r="U5" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" s="4">
         <v>3</v>
       </c>
       <c r="X5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>1</v>
+      </c>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1328,8 +1357,9 @@
       <c r="AM5" s="4"/>
       <c r="AN5" s="4"/>
       <c r="AO5" s="4"/>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP5" s="4"/>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1340,24 +1370,26 @@
         <v>4991815</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>46147</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>72</v>
       </c>
-      <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1366,25 +1398,25 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="4">
-        <v>1</v>
-      </c>
+      <c r="S6" s="4"/>
       <c r="T6" s="4">
         <v>1</v>
       </c>
       <c r="U6" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V6" s="4">
         <v>3</v>
       </c>
       <c r="W6" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X6" s="4">
         <v>2</v>
       </c>
-      <c r="Y6" s="4"/>
+      <c r="Y6" s="4">
+        <v>2</v>
+      </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
@@ -1401,8 +1433,9 @@
       <c r="AM6" s="4"/>
       <c r="AN6" s="4"/>
       <c r="AO6" s="4"/>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP6" s="4"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1412,52 +1445,54 @@
       <c r="C7" s="5">
         <v>5009739</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="5">
         <v>43632407</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <v>46142</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>120</v>
       </c>
-      <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
-      <c r="P7" s="4">
-        <v>1</v>
-      </c>
+      <c r="P7" s="4"/>
       <c r="Q7" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R7" s="4">
         <v>2</v>
       </c>
       <c r="S7" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" s="4">
         <v>1</v>
       </c>
-      <c r="W7" s="4"/>
+      <c r="W7" s="4">
+        <v>1</v>
+      </c>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
@@ -1476,8 +1511,9 @@
       <c r="AM7" s="4"/>
       <c r="AN7" s="4"/>
       <c r="AO7" s="4"/>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP7" s="4"/>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1487,52 +1523,54 @@
       <c r="C8" s="5">
         <v>6932240</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="5">
         <v>43559375</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>46142</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>72</v>
       </c>
-      <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="4">
-        <v>1</v>
-      </c>
+      <c r="P8" s="4"/>
       <c r="Q8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" s="4">
         <v>2</v>
       </c>
       <c r="S8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8" s="4">
         <v>1</v>
       </c>
-      <c r="W8" s="4"/>
+      <c r="W8" s="4">
+        <v>1</v>
+      </c>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
@@ -1551,8 +1589,9 @@
       <c r="AM8" s="4"/>
       <c r="AN8" s="4"/>
       <c r="AO8" s="4"/>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP8" s="4"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1562,36 +1601,36 @@
       <c r="C9" s="5">
         <v>7021837</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E9" s="5">
         <v>43286101</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>46172</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>144</v>
       </c>
-      <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4">
-        <v>2</v>
-      </c>
+      <c r="Q9" s="4"/>
       <c r="R9" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S9" s="4">
         <v>3</v>
@@ -1600,9 +1639,11 @@
         <v>3</v>
       </c>
       <c r="U9" s="4">
-        <v>1</v>
-      </c>
-      <c r="V9" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="V9" s="4">
+        <v>1</v>
+      </c>
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
@@ -1622,8 +1663,9 @@
       <c r="AM9" s="4"/>
       <c r="AN9" s="4"/>
       <c r="AO9" s="4"/>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP9" s="4"/>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>10</v>
       </c>
@@ -1633,34 +1675,34 @@
       <c r="C10" s="5">
         <v>7283002</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="5">
         <v>43306412</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>46132</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24</v>
       </c>
-      <c r="J10" s="4"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="4">
-        <v>1</v>
-      </c>
+      <c r="L10" s="4"/>
       <c r="M10" s="4">
         <v>1</v>
       </c>
       <c r="N10" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="4">
         <v>2</v>
@@ -1674,7 +1716,9 @@
       <c r="R10" s="4">
         <v>2</v>
       </c>
-      <c r="S10" s="4"/>
+      <c r="S10" s="4">
+        <v>2</v>
+      </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
       <c r="V10" s="4"/>
@@ -1697,8 +1741,9 @@
       <c r="AM10" s="4"/>
       <c r="AN10" s="4"/>
       <c r="AO10" s="4"/>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP10" s="4"/>
+    </row>
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>11</v>
       </c>
@@ -1708,50 +1753,52 @@
       <c r="C11" s="5">
         <v>7283001</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="5">
         <v>43336749</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>46132</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>12</v>
       </c>
-      <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
-      <c r="Q11" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q11" s="4"/>
       <c r="R11" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S11" s="4">
         <v>3</v>
       </c>
       <c r="T11" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U11" s="4">
         <v>2</v>
       </c>
       <c r="V11" s="4">
-        <v>1</v>
-      </c>
-      <c r="W11" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="W11" s="4">
+        <v>1</v>
+      </c>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
@@ -1770,8 +1817,9 @@
       <c r="AM11" s="4"/>
       <c r="AN11" s="4"/>
       <c r="AO11" s="4"/>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP11" s="4"/>
+    </row>
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>12</v>
       </c>
@@ -1781,46 +1829,48 @@
       <c r="C12" s="5">
         <v>7283003</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="5">
         <v>43213474</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="6">
+      <c r="H12" s="6">
         <v>46132</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48</v>
       </c>
-      <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="4">
-        <v>1</v>
-      </c>
+      <c r="M12" s="4"/>
       <c r="N12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" s="4">
         <v>3</v>
       </c>
       <c r="Q12" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" s="4">
-        <v>1</v>
-      </c>
-      <c r="S12" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="S12" s="4">
+        <v>1</v>
+      </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
@@ -1843,8 +1893,9 @@
       <c r="AM12" s="4"/>
       <c r="AN12" s="4"/>
       <c r="AO12" s="4"/>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP12" s="4"/>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>13</v>
       </c>
@@ -1854,34 +1905,34 @@
       <c r="C13" s="5">
         <v>7268502</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="5">
         <v>43649393</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="6">
+      <c r="H13" s="6">
         <v>46132</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <v>36</v>
       </c>
-      <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="4">
-        <v>1</v>
-      </c>
+      <c r="L13" s="4"/>
       <c r="M13" s="4">
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4">
         <v>2</v>
@@ -1895,7 +1946,9 @@
       <c r="R13" s="4">
         <v>2</v>
       </c>
-      <c r="S13" s="4"/>
+      <c r="S13" s="4">
+        <v>2</v>
+      </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
@@ -1918,8 +1971,9 @@
       <c r="AM13" s="4"/>
       <c r="AN13" s="4"/>
       <c r="AO13" s="4"/>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP13" s="4"/>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>14</v>
       </c>
@@ -1929,49 +1983,51 @@
       <c r="C14" s="5">
         <v>5235628</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="5">
         <v>43632407</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="6">
+      <c r="H14" s="6">
         <v>46103</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>108</v>
       </c>
-      <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="4">
-        <v>1</v>
-      </c>
+      <c r="P14" s="4"/>
       <c r="Q14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S14" s="4">
         <v>3</v>
       </c>
       <c r="T14" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" s="4">
-        <v>1</v>
-      </c>
-      <c r="V14" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="V14" s="4">
+        <v>1</v>
+      </c>
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
@@ -1991,8 +2047,9 @@
       <c r="AM14" s="4"/>
       <c r="AN14" s="4"/>
       <c r="AO14" s="4"/>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP14" s="4"/>
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>15</v>
       </c>
@@ -2002,50 +2059,52 @@
       <c r="C15" s="5">
         <v>7254752</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="5">
         <v>43299316</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G15" s="6">
+      <c r="H15" s="6">
         <v>46104</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>48</v>
       </c>
-      <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
-      <c r="Q15" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q15" s="4"/>
       <c r="R15" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S15" s="4">
         <v>3</v>
       </c>
       <c r="T15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U15" s="4">
         <v>2</v>
       </c>
       <c r="V15" s="4">
-        <v>1</v>
-      </c>
-      <c r="W15" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="W15" s="4">
+        <v>1</v>
+      </c>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
@@ -2064,8 +2123,9 @@
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
       <c r="AO15" s="4"/>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP15" s="4"/>
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>16</v>
       </c>
@@ -2075,49 +2135,51 @@
       <c r="C16" s="5">
         <v>7263895</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="5">
         <v>43418328</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="6">
+      <c r="H16" s="6">
         <v>46103</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>108</v>
       </c>
-      <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="4">
-        <v>1</v>
-      </c>
+      <c r="P16" s="4"/>
       <c r="Q16" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" s="4">
         <v>3</v>
       </c>
       <c r="T16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" s="4">
-        <v>1</v>
-      </c>
-      <c r="V16" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="V16" s="4">
+        <v>1</v>
+      </c>
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
@@ -2137,8 +2199,9 @@
       <c r="AM16" s="4"/>
       <c r="AN16" s="4"/>
       <c r="AO16" s="4"/>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP16" s="4"/>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>17</v>
       </c>
@@ -2148,50 +2211,52 @@
       <c r="C17" s="5">
         <v>5226145</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="5">
         <v>43697386</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="6">
+      <c r="H17" s="6">
         <v>46104</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>60</v>
       </c>
-      <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
-      <c r="Q17" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q17" s="4"/>
       <c r="R17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T17" s="4">
         <v>3</v>
       </c>
       <c r="U17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V17" s="4">
-        <v>1</v>
-      </c>
-      <c r="W17" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="W17" s="4">
+        <v>1</v>
+      </c>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
@@ -2210,8 +2275,9 @@
       <c r="AM17" s="4"/>
       <c r="AN17" s="4"/>
       <c r="AO17" s="4"/>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP17" s="4"/>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>18</v>
       </c>
@@ -2221,25 +2287,27 @@
       <c r="C18" s="5">
         <v>5235626</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="5">
         <v>43242437</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="6">
+      <c r="H18" s="6">
         <v>46103</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>48</v>
       </c>
-      <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -2250,25 +2318,25 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="4">
-        <v>1</v>
-      </c>
+      <c r="U18" s="4"/>
       <c r="V18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X18" s="4">
         <v>3</v>
       </c>
       <c r="Y18" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z18" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>1</v>
+      </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
@@ -2283,8 +2351,9 @@
       <c r="AM18" s="4"/>
       <c r="AN18" s="4"/>
       <c r="AO18" s="4"/>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP18" s="4"/>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>19</v>
       </c>
@@ -2294,25 +2363,27 @@
       <c r="C19" s="5">
         <v>5235627</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="5">
         <v>43358451</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G19" s="6">
+      <c r="H19" s="6">
         <v>46103</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>48</v>
       </c>
-      <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -2323,25 +2394,25 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="4">
-        <v>1</v>
-      </c>
+      <c r="U19" s="4"/>
       <c r="V19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W19" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X19" s="4">
         <v>3</v>
       </c>
       <c r="Y19" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z19" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>1</v>
+      </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
@@ -2356,8 +2427,9 @@
       <c r="AM19" s="4"/>
       <c r="AN19" s="4"/>
       <c r="AO19" s="4"/>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP19" s="4"/>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>20</v>
       </c>
@@ -2367,25 +2439,27 @@
       <c r="C20" s="5">
         <v>5060906</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="5">
         <v>54111405</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="6">
+      <c r="H20" s="6">
         <v>46172</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="I20" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>144</v>
       </c>
-      <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2402,25 +2476,25 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
-      <c r="AA20" s="4">
-        <v>1</v>
-      </c>
+      <c r="AA20" s="4"/>
       <c r="AB20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD20" s="4">
         <v>3</v>
       </c>
       <c r="AE20" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" s="4">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="AG20" s="4">
+        <v>1</v>
+      </c>
       <c r="AH20" s="4"/>
       <c r="AI20" s="4"/>
       <c r="AJ20" s="4"/>
@@ -2429,8 +2503,9 @@
       <c r="AM20" s="4"/>
       <c r="AN20" s="4"/>
       <c r="AO20" s="4"/>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP20" s="4"/>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>21</v>
       </c>
@@ -2440,25 +2515,27 @@
       <c r="C21" s="5">
         <v>6874170</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="5">
         <v>43758365</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="6">
+      <c r="H21" s="6">
         <v>46142</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>60</v>
       </c>
-      <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2468,19 +2545,19 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
-      <c r="T21" s="4">
-        <v>1</v>
-      </c>
+      <c r="T21" s="4"/>
       <c r="U21" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21" s="4">
         <v>2</v>
       </c>
       <c r="W21" s="4">
-        <v>1</v>
-      </c>
-      <c r="X21" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="X21" s="4">
+        <v>1</v>
+      </c>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
@@ -2498,8 +2575,9 @@
       <c r="AM21" s="4"/>
       <c r="AN21" s="4"/>
       <c r="AO21" s="4"/>
-    </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP21" s="4"/>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>22</v>
       </c>
@@ -2510,24 +2588,26 @@
         <v>791970</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="6">
+      <c r="H22" s="6">
         <v>46196</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>120</v>
       </c>
-      <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2552,23 +2632,24 @@
       <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
-      <c r="AI22" s="4">
-        <v>1</v>
-      </c>
+      <c r="AI22" s="4"/>
       <c r="AJ22" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK22" s="4">
         <v>2</v>
       </c>
       <c r="AL22" s="4">
-        <v>1</v>
-      </c>
-      <c r="AM22" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="AM22" s="4">
+        <v>1</v>
+      </c>
       <c r="AN22" s="4"/>
       <c r="AO22" s="4"/>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP22" s="4"/>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>23</v>
       </c>
@@ -2579,24 +2660,26 @@
         <v>793473</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G23" s="6">
+      <c r="H23" s="6">
         <v>46076</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>240</v>
       </c>
-      <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2626,12 +2709,13 @@
       <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="4" t="s">
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AO23" s="4"/>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP23" s="4"/>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>24</v>
       </c>
@@ -2642,24 +2726,26 @@
         <v>1251823</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="6">
+      <c r="H24" s="6">
         <v>46045</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>96</v>
       </c>
-      <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2688,13 +2774,14 @@
       <c r="AJ24" s="4"/>
       <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
-      <c r="AM24" s="4" t="s">
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="AN24" s="4"/>
       <c r="AO24" s="4"/>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP24" s="4"/>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>25</v>
       </c>
@@ -2704,25 +2791,27 @@
       <c r="C25" s="5">
         <v>7268502</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E25" s="5">
         <v>43341472</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G25" s="6">
+      <c r="H25" s="6">
         <v>46132</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J25" s="3">
         <v>60</v>
       </c>
-      <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -2734,22 +2823,22 @@
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
-      <c r="V25" s="4">
-        <v>2</v>
-      </c>
+      <c r="V25" s="4"/>
       <c r="W25" s="4">
         <v>2</v>
       </c>
       <c r="X25" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y25" s="4">
         <v>3</v>
       </c>
       <c r="Z25" s="4">
-        <v>2</v>
-      </c>
-      <c r="AA25" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="AA25" s="4">
+        <v>2</v>
+      </c>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
       <c r="AD25" s="4"/>
@@ -2764,9 +2853,10 @@
       <c r="AM25" s="4"/>
       <c r="AN25" s="4"/>
       <c r="AO25" s="4"/>
+      <c r="AP25" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:Z25" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
+  <autoFilter ref="B1:AA25" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E067214F-6196-45E7-8DB8-A5ACF8EDB13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18C66AD-B1CC-4359-965B-9DE621942103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -1404,7 +1404,82 @@
       <c r="AP7" s="4"/>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C8" s="12"/>
+      <c r="A8" s="5">
+        <v>325</v>
+      </c>
+      <c r="B8" s="5">
+        <v>13137558</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5215316</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="5">
+        <v>43242437</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="6">
+        <v>46141</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="3">
+        <v>60</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4">
+        <v>1</v>
+      </c>
+      <c r="W8" s="4">
+        <v>3</v>
+      </c>
+      <c r="X8" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AF8" s="4"/>
+      <c r="AG8" s="4"/>
+      <c r="AH8" s="4"/>
+      <c r="AI8" s="4"/>
+      <c r="AJ8" s="4"/>
+      <c r="AK8" s="4"/>
+      <c r="AL8" s="4"/>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+      <c r="AP8" s="4"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C9" s="12"/>
@@ -1524,7 +1599,7 @@
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B7">
+  <conditionalFormatting sqref="B2:B8">
     <cfRule type="duplicateValues" dxfId="0" priority="112"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18C66AD-B1CC-4359-965B-9DE621942103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A919164C-C0D8-4511-BF88-2B241004A351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559AE16B-4D63-4060-81A6-1E3E42399F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5C42A1-7313-49DC-AB9E-C30F223E8AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="DISPO" sheetId="3" r:id="rId1"/>
     <sheet name="Planilha2" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DISPO!$B$1:$AA$6</definedName>
   </definedNames>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="110">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -270,10 +273,106 @@
     <t>EROS 2 INFANTIL</t>
   </si>
   <si>
-    <t>AZABA</t>
-  </si>
-  <si>
-    <t>CZASTE</t>
+    <t>VERSA</t>
+  </si>
+  <si>
+    <t>BGMVML</t>
+  </si>
+  <si>
+    <t>BRUMA</t>
+  </si>
+  <si>
+    <t>PRETO</t>
+  </si>
+  <si>
+    <t>SAFIRA</t>
+  </si>
+  <si>
+    <t>RUSH</t>
+  </si>
+  <si>
+    <t>MARTE</t>
+  </si>
+  <si>
+    <t>PT/DRD</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>SERENO</t>
+  </si>
+  <si>
+    <t>ATMOS</t>
+  </si>
+  <si>
+    <t>DAY</t>
+  </si>
+  <si>
+    <t>CHUMBO</t>
+  </si>
+  <si>
+    <t>EROS 2</t>
+  </si>
+  <si>
+    <t>BRANCO</t>
+  </si>
+  <si>
+    <t>ACQUA</t>
+  </si>
+  <si>
+    <t>MRHO</t>
+  </si>
+  <si>
+    <t>FLUTUA 2</t>
+  </si>
+  <si>
+    <t>LUMI</t>
+  </si>
+  <si>
+    <t>DYNAMIC / 343</t>
+  </si>
+  <si>
+    <t>MRHDRD</t>
+  </si>
+  <si>
+    <t>MILITR</t>
+  </si>
+  <si>
+    <t>ALGPSC</t>
+  </si>
+  <si>
+    <t>APOLIS</t>
+  </si>
+  <si>
+    <t>BRSMRT</t>
+  </si>
+  <si>
+    <t>DAY / 547</t>
+  </si>
+  <si>
+    <t>STOAMS</t>
+  </si>
+  <si>
+    <t>LUNAR</t>
+  </si>
+  <si>
+    <t>ATMOS /101</t>
+  </si>
+  <si>
+    <t>ARTPES</t>
+  </si>
+  <si>
+    <t>STREAM INFANTIL</t>
+  </si>
+  <si>
+    <t>PT/VMH</t>
+  </si>
+  <si>
+    <t>CHBHIB</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -379,7 +478,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -402,13 +501,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -444,6 +569,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -484,6 +621,419 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Encomendas_SIN_ARTIGO"/>
+      <sheetName val="Planilha2"/>
+      <sheetName val="Planilha1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="D1" t="str">
+            <v>Nr.Enc. GCI</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v>Empresa</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="D2">
+            <v>5013559</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="D3">
+            <v>5013428</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="D4">
+            <v>6913394</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="D5">
+            <v>4993104</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="D6">
+            <v>4993151</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="D7">
+            <v>6913394</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="D8">
+            <v>7228507</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="D9">
+            <v>4993151</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10">
+            <v>4993104</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11">
+            <v>4993151</v>
+          </cell>
+          <cell r="E11" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="D12">
+            <v>4993104</v>
+          </cell>
+          <cell r="E12" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="D13">
+            <v>4993151</v>
+          </cell>
+          <cell r="E13" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="D14">
+            <v>6913394</v>
+          </cell>
+          <cell r="E14" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="D15">
+            <v>4993104</v>
+          </cell>
+          <cell r="E15" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="D16">
+            <v>4993151</v>
+          </cell>
+          <cell r="E16" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="D17">
+            <v>4993104</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="D18">
+            <v>6913394</v>
+          </cell>
+          <cell r="E18" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19">
+            <v>4993104</v>
+          </cell>
+          <cell r="E19" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="D20">
+            <v>4993151</v>
+          </cell>
+          <cell r="E20" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="D21">
+            <v>6913394</v>
+          </cell>
+          <cell r="E21" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="D22">
+            <v>5038292</v>
+          </cell>
+          <cell r="E22" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="D23">
+            <v>5215318</v>
+          </cell>
+          <cell r="E23" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="D24">
+            <v>5215319</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="D25">
+            <v>5215309</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>5274759</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
+            <v>7426392</v>
+          </cell>
+          <cell r="E27" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="D28">
+            <v>7426388</v>
+          </cell>
+          <cell r="E28" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="D29">
+            <v>7268503</v>
+          </cell>
+          <cell r="E29" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="D30">
+            <v>7426399</v>
+          </cell>
+          <cell r="E30" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="D31">
+            <v>7426391</v>
+          </cell>
+          <cell r="E31" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="D32">
+            <v>5199180</v>
+          </cell>
+          <cell r="E32" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="D33">
+            <v>5274744</v>
+          </cell>
+          <cell r="E33" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="D34">
+            <v>5269321</v>
+          </cell>
+          <cell r="E34" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="D35">
+            <v>5269320</v>
+          </cell>
+          <cell r="E35" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="D36">
+            <v>5269322</v>
+          </cell>
+          <cell r="E36" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="D37">
+            <v>5274753</v>
+          </cell>
+          <cell r="E37" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="D38">
+            <v>5259457</v>
+          </cell>
+          <cell r="E38" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="D39">
+            <v>5274754</v>
+          </cell>
+          <cell r="E39" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="D40">
+            <v>5274747</v>
+          </cell>
+          <cell r="E40" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="D41">
+            <v>7372755</v>
+          </cell>
+          <cell r="E41" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="D42">
+            <v>7372771</v>
+          </cell>
+          <cell r="E42" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="D43">
+            <v>7426389</v>
+          </cell>
+          <cell r="E43" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="D44">
+            <v>5274741</v>
+          </cell>
+          <cell r="E44" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="D45">
+            <v>5274761</v>
+          </cell>
+          <cell r="E45" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="D46">
+            <v>7426398</v>
+          </cell>
+          <cell r="E46" t="str">
+            <v>VULTS</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="D47">
+            <v>4993370</v>
+          </cell>
+          <cell r="E47" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="D48">
+            <v>4993371</v>
+          </cell>
+          <cell r="E48" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="D49">
+            <v>4993255</v>
+          </cell>
+          <cell r="E49" t="str">
+            <v>AZABA</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -812,7 +1362,7 @@
     <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" style="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="22" width="3.42578125" customWidth="1"/>
@@ -956,29 +1506,30 @@
         <v>57</v>
       </c>
       <c r="B2" s="5">
-        <v>13137448</v>
+        <v>13263501</v>
       </c>
       <c r="C2" s="5">
-        <v>5215309</v>
-      </c>
-      <c r="D2" s="5" t="s">
+        <v>5274741</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <f>VLOOKUP(C2,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E2" s="5">
+        <v>43752263</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="5">
-        <v>43263432</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H2" s="6">
-        <v>46113</v>
-      </c>
-      <c r="I2" s="6"/>
+        <v>46147</v>
+      </c>
+      <c r="I2" s="13"/>
       <c r="J2" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -986,29 +1537,33 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4">
-        <v>1</v>
-      </c>
-      <c r="R2" s="4">
-        <v>2</v>
-      </c>
-      <c r="S2" s="4">
-        <v>3</v>
-      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
       <c r="T2" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" s="4">
-        <v>1</v>
-      </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="W2" s="4">
+        <v>2</v>
+      </c>
+      <c r="X2" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>1</v>
+      </c>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
       <c r="AD2" s="4"/>
@@ -1030,44 +1585,39 @@
         <v>314</v>
       </c>
       <c r="B3" s="5">
-        <v>13249326</v>
+        <v>12790961</v>
       </c>
       <c r="C3" s="5">
-        <v>5269322</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>76</v>
+        <v>5013428</v>
+      </c>
+      <c r="D3" s="5" t="str">
+        <f>VLOOKUP(C3,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
       </c>
       <c r="E3" s="5">
-        <v>43406455</v>
+        <v>43632407</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="H3" s="6">
-        <v>46114</v>
-      </c>
-      <c r="I3" s="6"/>
+        <v>46172</v>
+      </c>
+      <c r="I3" s="13"/>
       <c r="J3" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="4">
-        <v>1</v>
-      </c>
-      <c r="O3" s="4">
-        <v>1</v>
-      </c>
-      <c r="P3" s="4">
-        <v>2</v>
-      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
       <c r="Q3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R3" s="4">
         <v>2</v>
@@ -1075,10 +1625,18 @@
       <c r="S3" s="4">
         <v>2</v>
       </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
+      <c r="T3" s="4">
+        <v>3</v>
+      </c>
+      <c r="U3" s="4">
+        <v>2</v>
+      </c>
+      <c r="V3" s="4">
+        <v>1</v>
+      </c>
+      <c r="W3" s="4">
+        <v>1</v>
+      </c>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="4"/>
@@ -1104,54 +1662,55 @@
         <v>316</v>
       </c>
       <c r="B4" s="5">
-        <v>13249325</v>
+        <v>12791194</v>
       </c>
       <c r="C4" s="5">
-        <v>5269320</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>76</v>
+        <v>5013559</v>
+      </c>
+      <c r="D4" s="5" t="str">
+        <f>VLOOKUP(C4,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
       </c>
       <c r="E4" s="5">
-        <v>43406455</v>
+        <v>43608374</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="H4" s="6">
-        <v>46114</v>
-      </c>
-      <c r="I4" s="6"/>
+        <v>46150</v>
+      </c>
+      <c r="I4" s="13"/>
       <c r="J4" s="3">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="4">
-        <v>1</v>
-      </c>
-      <c r="O4" s="4">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4">
-        <v>2</v>
-      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
       <c r="Q4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="4">
         <v>2</v>
       </c>
       <c r="S4" s="4">
-        <v>2</v>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="T4" s="4">
+        <v>3</v>
+      </c>
+      <c r="U4" s="4">
+        <v>2</v>
+      </c>
+      <c r="V4" s="4">
+        <v>1</v>
+      </c>
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
@@ -1178,59 +1737,70 @@
         <v>322</v>
       </c>
       <c r="B5" s="5">
-        <v>13249317</v>
+        <v>13224179</v>
       </c>
       <c r="C5" s="5">
-        <v>5269321</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>76</v>
+        <v>7372755</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f>VLOOKUP(C5,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
       </c>
       <c r="E5" s="5">
-        <v>43406455</v>
+        <v>43667419</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="H5" s="6">
-        <v>46114</v>
-      </c>
-      <c r="I5" s="6"/>
+        <v>46162</v>
+      </c>
+      <c r="I5" s="13"/>
       <c r="J5" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="4">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="4">
-        <v>2</v>
-      </c>
-      <c r="R5" s="4">
-        <v>2</v>
-      </c>
-      <c r="S5" s="4">
-        <v>2</v>
-      </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="V5" s="4">
+        <v>1</v>
+      </c>
+      <c r="W5" s="4">
+        <v>2</v>
+      </c>
+      <c r="X5" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>1</v>
+      </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
@@ -1252,29 +1822,30 @@
         <v>323</v>
       </c>
       <c r="B6" s="5">
-        <v>13137456</v>
+        <v>13224181</v>
       </c>
       <c r="C6" s="5">
-        <v>5215318</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>76</v>
+        <v>7372771</v>
+      </c>
+      <c r="D6" s="5" t="str">
+        <f>VLOOKUP(C6,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
       </c>
       <c r="E6" s="5">
-        <v>43242437</v>
+        <v>43667419</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="H6" s="6">
-        <v>46141</v>
-      </c>
-      <c r="I6" s="6"/>
+        <v>46193</v>
+      </c>
+      <c r="I6" s="13"/>
       <c r="J6" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -1282,32 +1853,38 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
+      <c r="Q6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R6" s="4">
+        <v>2</v>
+      </c>
+      <c r="S6" s="4">
+        <v>3</v>
+      </c>
       <c r="T6" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U6" s="4">
-        <v>1</v>
-      </c>
-      <c r="V6" s="4">
-        <v>2</v>
-      </c>
-      <c r="W6" s="4">
-        <v>2</v>
-      </c>
-      <c r="X6" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="W6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1327,32 +1904,33 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" s="5">
-        <v>13137557</v>
+        <v>13224114</v>
       </c>
       <c r="C7" s="5">
-        <v>5215319</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>76</v>
+        <v>5259457</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f>VLOOKUP(C7,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
       </c>
       <c r="E7" s="5">
-        <v>43242437</v>
+        <v>43608374</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="H7" s="6">
-        <v>46202</v>
-      </c>
-      <c r="I7" s="6"/>
+        <v>46193</v>
+      </c>
+      <c r="I7" s="13"/>
       <c r="J7" s="3">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1360,32 +1938,38 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
+      <c r="Q7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="S7" s="4">
+        <v>2</v>
+      </c>
       <c r="T7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V7" s="4">
         <v>2</v>
       </c>
       <c r="W7" s="4">
-        <v>2</v>
-      </c>
-      <c r="X7" s="4">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="4">
-        <v>2</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA7" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -1405,32 +1989,33 @@
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B8" s="5">
-        <v>13137558</v>
+        <v>13109256</v>
       </c>
       <c r="C8" s="5">
-        <v>5215316</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>76</v>
+        <v>5199180</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f>VLOOKUP(C8,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
       </c>
       <c r="E8" s="5">
-        <v>43242437</v>
+        <v>43395156</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H8" s="6">
-        <v>46141</v>
-      </c>
-      <c r="I8" s="6"/>
+        <v>46165</v>
+      </c>
+      <c r="I8" s="13"/>
       <c r="J8" s="3">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -1441,9 +2026,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="4">
-        <v>1</v>
-      </c>
+      <c r="T8" s="4"/>
       <c r="U8" s="4">
         <v>1</v>
       </c>
@@ -1451,13 +2034,13 @@
         <v>1</v>
       </c>
       <c r="W8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X8" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z8" s="4">
         <v>1</v>
@@ -1482,111 +2065,2395 @@
       <c r="AP8" s="4"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C9" s="12"/>
+      <c r="A9" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="14">
+        <v>12837174</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5038292</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f>VLOOKUP(C9,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E9" s="14">
+        <v>54104269</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="6">
+        <v>46158</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="3">
+        <v>48</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4">
+        <v>2</v>
+      </c>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4">
+        <v>5</v>
+      </c>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4"/>
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
+      <c r="AL9" s="4"/>
+      <c r="AM9" s="4"/>
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4"/>
+      <c r="AP9" s="4"/>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C10" s="12"/>
+      <c r="A10" s="14">
+        <v>334</v>
+      </c>
+      <c r="B10" s="14">
+        <v>12757541</v>
+      </c>
+      <c r="C10" s="5">
+        <v>6913394</v>
+      </c>
+      <c r="D10" s="5" t="str">
+        <f>VLOOKUP(C10,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E10" s="14">
+        <v>43286101</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="3">
+        <v>120</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4">
+        <v>1</v>
+      </c>
+      <c r="R10" s="4">
+        <v>2</v>
+      </c>
+      <c r="S10" s="4">
+        <v>2</v>
+      </c>
+      <c r="T10" s="4">
+        <v>3</v>
+      </c>
+      <c r="U10" s="4">
+        <v>2</v>
+      </c>
+      <c r="V10" s="4">
+        <v>1</v>
+      </c>
+      <c r="W10" s="4">
+        <v>1</v>
+      </c>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AF10" s="4"/>
+      <c r="AG10" s="4"/>
+      <c r="AH10" s="4"/>
+      <c r="AI10" s="4"/>
+      <c r="AJ10" s="4"/>
+      <c r="AK10" s="4"/>
+      <c r="AL10" s="4"/>
+      <c r="AM10" s="4"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4"/>
+      <c r="AP10" s="4"/>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C11" s="12"/>
+      <c r="A11" s="14">
+        <v>335</v>
+      </c>
+      <c r="B11" s="14">
+        <v>12757541</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6913394</v>
+      </c>
+      <c r="D11" s="5" t="str">
+        <f>VLOOKUP(C11,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E11" s="14">
+        <v>43286101</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="3">
+        <v>108</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4">
+        <v>1</v>
+      </c>
+      <c r="S11" s="4">
+        <v>3</v>
+      </c>
+      <c r="T11" s="4">
+        <v>3</v>
+      </c>
+      <c r="U11" s="4">
+        <v>2</v>
+      </c>
+      <c r="V11" s="4">
+        <v>1</v>
+      </c>
+      <c r="W11" s="4">
+        <v>1</v>
+      </c>
+      <c r="X11" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AF11" s="4"/>
+      <c r="AG11" s="4"/>
+      <c r="AH11" s="4"/>
+      <c r="AI11" s="4"/>
+      <c r="AJ11" s="4"/>
+      <c r="AK11" s="4"/>
+      <c r="AL11" s="4"/>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C12" s="12"/>
+      <c r="A12" s="14">
+        <v>336</v>
+      </c>
+      <c r="B12" s="14">
+        <v>12757541</v>
+      </c>
+      <c r="C12" s="5">
+        <v>6913394</v>
+      </c>
+      <c r="D12" s="5" t="str">
+        <f>VLOOKUP(C12,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E12" s="14">
+        <v>43927547</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="3">
+        <v>36</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4">
+        <v>1</v>
+      </c>
+      <c r="R12" s="4">
+        <v>2</v>
+      </c>
+      <c r="S12" s="4">
+        <v>2</v>
+      </c>
+      <c r="T12" s="4">
+        <v>3</v>
+      </c>
+      <c r="U12" s="4">
+        <v>2</v>
+      </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
+      <c r="W12" s="4">
+        <v>1</v>
+      </c>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AG12" s="4"/>
+      <c r="AH12" s="4"/>
+      <c r="AI12" s="4"/>
+      <c r="AJ12" s="4"/>
+      <c r="AK12" s="4"/>
+      <c r="AL12" s="4"/>
+      <c r="AM12" s="4"/>
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C13" s="12"/>
+      <c r="A13" s="14">
+        <v>339</v>
+      </c>
+      <c r="B13" s="14">
+        <v>12757770</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4993151</v>
+      </c>
+      <c r="D13" s="5" t="str">
+        <f>VLOOKUP(C13,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E13" s="14">
+        <v>43409454</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="3">
+        <v>12</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4">
+        <v>1</v>
+      </c>
+      <c r="U13" s="4">
+        <v>1</v>
+      </c>
+      <c r="V13" s="4">
+        <v>3</v>
+      </c>
+      <c r="W13" s="4">
+        <v>3</v>
+      </c>
+      <c r="X13" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
+      <c r="AH13" s="4"/>
+      <c r="AI13" s="4"/>
+      <c r="AJ13" s="4"/>
+      <c r="AK13" s="4"/>
+      <c r="AL13" s="4"/>
+      <c r="AM13" s="4"/>
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="4"/>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C14" s="12"/>
+      <c r="A14" s="14">
+        <v>340</v>
+      </c>
+      <c r="B14" s="14">
+        <v>12757770</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4993151</v>
+      </c>
+      <c r="D14" s="5" t="str">
+        <f>VLOOKUP(C14,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E14" s="14">
+        <v>43752263</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="3">
+        <v>48</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4">
+        <v>1</v>
+      </c>
+      <c r="V14" s="4">
+        <v>2</v>
+      </c>
+      <c r="W14" s="4">
+        <v>3</v>
+      </c>
+      <c r="X14" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="4">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
+      <c r="AH14" s="4"/>
+      <c r="AI14" s="4"/>
+      <c r="AJ14" s="4"/>
+      <c r="AK14" s="4"/>
+      <c r="AL14" s="4"/>
+      <c r="AM14" s="4"/>
+      <c r="AN14" s="4"/>
+      <c r="AO14" s="4"/>
+      <c r="AP14" s="4"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C15" s="12"/>
+      <c r="A15" s="14">
+        <v>341</v>
+      </c>
+      <c r="B15" s="14">
+        <v>13140161</v>
+      </c>
+      <c r="C15" s="5">
+        <v>7228507</v>
+      </c>
+      <c r="D15" s="5" t="str">
+        <f>VLOOKUP(C15,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E15" s="14">
+        <v>43299316</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I15" s="13"/>
+      <c r="J15" s="3">
+        <v>108</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4">
+        <v>1</v>
+      </c>
+      <c r="R15" s="4">
+        <v>2</v>
+      </c>
+      <c r="S15" s="4">
+        <v>3</v>
+      </c>
+      <c r="T15" s="4">
+        <v>3</v>
+      </c>
+      <c r="U15" s="4">
+        <v>2</v>
+      </c>
+      <c r="V15" s="4">
+        <v>1</v>
+      </c>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="4"/>
+      <c r="AF15" s="4"/>
+      <c r="AG15" s="4"/>
+      <c r="AH15" s="4"/>
+      <c r="AI15" s="4"/>
+      <c r="AJ15" s="4"/>
+      <c r="AK15" s="4"/>
+      <c r="AL15" s="4"/>
+      <c r="AM15" s="4"/>
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="4"/>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C16" s="12"/>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" s="12"/>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C18" s="12"/>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C19" s="12"/>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="12"/>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
-    </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C24" s="12"/>
-    </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C25" s="12"/>
-    </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C26" s="12"/>
-    </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C27" s="12"/>
-    </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C28" s="12"/>
-    </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C29" s="12"/>
-    </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C30" s="12"/>
-    </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C31" s="12"/>
-    </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C32" s="12"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="12"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="12"/>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="12"/>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="12"/>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="12"/>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="12"/>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <v>388</v>
+      </c>
+      <c r="B16" s="14">
+        <v>12757545</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4993104</v>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f>VLOOKUP(C16,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E16" s="14">
+        <v>43389459</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="3">
+        <v>48</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="4"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="4"/>
+      <c r="AH16" s="4"/>
+      <c r="AI16" s="4"/>
+      <c r="AJ16" s="4"/>
+      <c r="AK16" s="4"/>
+      <c r="AL16" s="4"/>
+      <c r="AM16" s="4"/>
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="4"/>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <v>390</v>
+      </c>
+      <c r="B17" s="14">
+        <v>12757893</v>
+      </c>
+      <c r="C17" s="5">
+        <v>4993255</v>
+      </c>
+      <c r="D17" s="5" t="str">
+        <f>VLOOKUP(C17,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E17" s="14">
+        <v>43632407</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" s="6">
+        <v>46172</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="3">
+        <v>48</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4">
+        <v>1</v>
+      </c>
+      <c r="S17" s="4">
+        <v>2</v>
+      </c>
+      <c r="T17" s="4">
+        <v>4</v>
+      </c>
+      <c r="U17" s="4">
+        <v>3</v>
+      </c>
+      <c r="V17" s="4">
+        <v>2</v>
+      </c>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="4"/>
+      <c r="AK17" s="4"/>
+      <c r="AL17" s="4"/>
+      <c r="AM17" s="4"/>
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="4"/>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>409</v>
+      </c>
+      <c r="B18" s="14">
+        <v>12758052</v>
+      </c>
+      <c r="C18" s="5">
+        <v>4993370</v>
+      </c>
+      <c r="D18" s="5" t="str">
+        <f>VLOOKUP(C18,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E18" s="14">
+        <v>43393460</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="6">
+        <v>46172</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="3">
+        <v>12</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4">
+        <v>1</v>
+      </c>
+      <c r="S18" s="4">
+        <v>2</v>
+      </c>
+      <c r="T18" s="4">
+        <v>4</v>
+      </c>
+      <c r="U18" s="4">
+        <v>3</v>
+      </c>
+      <c r="V18" s="4">
+        <v>2</v>
+      </c>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4"/>
+      <c r="AF18" s="4"/>
+      <c r="AG18" s="4"/>
+      <c r="AH18" s="4"/>
+      <c r="AI18" s="4"/>
+      <c r="AJ18" s="4"/>
+      <c r="AK18" s="4"/>
+      <c r="AL18" s="4"/>
+      <c r="AM18" s="4"/>
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="4"/>
+      <c r="AP18" s="4"/>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <v>412</v>
+      </c>
+      <c r="B19" s="14">
+        <v>12758063</v>
+      </c>
+      <c r="C19" s="5">
+        <v>4993371</v>
+      </c>
+      <c r="D19" s="5" t="str">
+        <f>VLOOKUP(C19,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E19" s="14">
+        <v>43393460</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="6">
+        <v>46172</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="3">
+        <v>12</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4">
+        <v>1</v>
+      </c>
+      <c r="S19" s="4">
+        <v>2</v>
+      </c>
+      <c r="T19" s="4">
+        <v>4</v>
+      </c>
+      <c r="U19" s="4">
+        <v>3</v>
+      </c>
+      <c r="V19" s="4">
+        <v>2</v>
+      </c>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4"/>
+      <c r="AF19" s="4"/>
+      <c r="AG19" s="4"/>
+      <c r="AH19" s="4"/>
+      <c r="AI19" s="4"/>
+      <c r="AJ19" s="4"/>
+      <c r="AK19" s="4"/>
+      <c r="AL19" s="4"/>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="4"/>
+      <c r="AO19" s="4"/>
+      <c r="AP19" s="4"/>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <v>424</v>
+      </c>
+      <c r="B20" s="14">
+        <v>13263562</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7426388</v>
+      </c>
+      <c r="D20" s="5" t="str">
+        <f>VLOOKUP(C20,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E20" s="14">
+        <v>43298343</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="3">
+        <v>180</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="U20" s="4">
+        <v>1</v>
+      </c>
+      <c r="V20" s="4">
+        <v>2</v>
+      </c>
+      <c r="W20" s="4">
+        <v>3</v>
+      </c>
+      <c r="X20" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z20" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB20" s="4"/>
+      <c r="AC20" s="4"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="4"/>
+      <c r="AF20" s="4"/>
+      <c r="AG20" s="4"/>
+      <c r="AH20" s="4"/>
+      <c r="AI20" s="4"/>
+      <c r="AJ20" s="4"/>
+      <c r="AK20" s="4"/>
+      <c r="AL20" s="4"/>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4"/>
+      <c r="AP20" s="4"/>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <v>426</v>
+      </c>
+      <c r="B21" s="14">
+        <v>13263499</v>
+      </c>
+      <c r="C21" s="5">
+        <v>5274744</v>
+      </c>
+      <c r="D21" s="5" t="str">
+        <f>VLOOKUP(C21,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E21" s="14">
+        <v>43395156</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H21" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="3">
+        <v>108</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="U21" s="4">
+        <v>1</v>
+      </c>
+      <c r="V21" s="4">
+        <v>2</v>
+      </c>
+      <c r="W21" s="4">
+        <v>3</v>
+      </c>
+      <c r="X21" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4"/>
+      <c r="AF21" s="4"/>
+      <c r="AG21" s="4"/>
+      <c r="AH21" s="4"/>
+      <c r="AI21" s="4"/>
+      <c r="AJ21" s="4"/>
+      <c r="AK21" s="4"/>
+      <c r="AL21" s="4"/>
+      <c r="AM21" s="4"/>
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4"/>
+      <c r="AP21" s="4"/>
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <v>427</v>
+      </c>
+      <c r="B22" s="14">
+        <v>13263552</v>
+      </c>
+      <c r="C22" s="5">
+        <v>7426389</v>
+      </c>
+      <c r="D22" s="5" t="str">
+        <f>VLOOKUP(C22,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E22" s="14">
+        <v>43667419</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I22" s="13"/>
+      <c r="J22" s="3">
+        <v>36</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R22" s="4">
+        <v>1</v>
+      </c>
+      <c r="S22" s="4">
+        <v>2</v>
+      </c>
+      <c r="T22" s="4">
+        <v>3</v>
+      </c>
+      <c r="U22" s="4">
+        <v>3</v>
+      </c>
+      <c r="V22" s="4">
+        <v>2</v>
+      </c>
+      <c r="W22" s="4">
+        <v>1</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AF22" s="4"/>
+      <c r="AG22" s="4"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="4"/>
+      <c r="AJ22" s="4"/>
+      <c r="AK22" s="4"/>
+      <c r="AL22" s="4"/>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A23" s="14">
+        <v>429</v>
+      </c>
+      <c r="B23" s="14">
+        <v>13263489</v>
+      </c>
+      <c r="C23" s="5">
+        <v>5274747</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f>VLOOKUP(C23,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E23" s="14">
+        <v>43616206</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="3">
+        <v>48</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R23" s="4">
+        <v>1</v>
+      </c>
+      <c r="S23" s="4">
+        <v>2</v>
+      </c>
+      <c r="T23" s="4">
+        <v>3</v>
+      </c>
+      <c r="U23" s="4">
+        <v>3</v>
+      </c>
+      <c r="V23" s="4">
+        <v>2</v>
+      </c>
+      <c r="W23" s="4">
+        <v>1</v>
+      </c>
+      <c r="X23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB23" s="4"/>
+      <c r="AC23" s="4"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="4"/>
+      <c r="AF23" s="4"/>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="4"/>
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="4"/>
+      <c r="AL23" s="4"/>
+      <c r="AM23" s="4"/>
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4"/>
+      <c r="AP23" s="4"/>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <v>436</v>
+      </c>
+      <c r="B24" s="14">
+        <v>13263547</v>
+      </c>
+      <c r="C24" s="5">
+        <v>7426398</v>
+      </c>
+      <c r="D24" s="5" t="str">
+        <f>VLOOKUP(C24,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E24" s="14">
+        <v>43927547</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="6">
+        <v>46178</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="3">
+        <v>48</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R24" s="4">
+        <v>1</v>
+      </c>
+      <c r="S24" s="4">
+        <v>2</v>
+      </c>
+      <c r="T24" s="4">
+        <v>3</v>
+      </c>
+      <c r="U24" s="4">
+        <v>3</v>
+      </c>
+      <c r="V24" s="4">
+        <v>2</v>
+      </c>
+      <c r="W24" s="4">
+        <v>1</v>
+      </c>
+      <c r="X24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="4"/>
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="4"/>
+      <c r="AP24" s="4"/>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A25" s="14">
+        <v>441</v>
+      </c>
+      <c r="B25" s="14">
+        <v>13263549</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7426399</v>
+      </c>
+      <c r="D25" s="5" t="str">
+        <f>VLOOKUP(C25,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E25" s="14">
+        <v>43299316</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="6">
+        <v>46178</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="3">
+        <v>60</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R25" s="4">
+        <v>1</v>
+      </c>
+      <c r="S25" s="4">
+        <v>2</v>
+      </c>
+      <c r="T25" s="4">
+        <v>3</v>
+      </c>
+      <c r="U25" s="4">
+        <v>3</v>
+      </c>
+      <c r="V25" s="4">
+        <v>2</v>
+      </c>
+      <c r="W25" s="4">
+        <v>1</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="4"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
+      <c r="AL25" s="4"/>
+      <c r="AM25" s="4"/>
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="4"/>
+      <c r="AP25" s="4"/>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <v>442</v>
+      </c>
+      <c r="B26" s="14">
+        <v>13263498</v>
+      </c>
+      <c r="C26" s="5">
+        <v>5274759</v>
+      </c>
+      <c r="D26" s="5" t="str">
+        <f>VLOOKUP(C26,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E26" s="14">
+        <v>43263432</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="6">
+        <v>46178</v>
+      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="3">
+        <v>36</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R26" s="4">
+        <v>1</v>
+      </c>
+      <c r="S26" s="4">
+        <v>2</v>
+      </c>
+      <c r="T26" s="4">
+        <v>3</v>
+      </c>
+      <c r="U26" s="4">
+        <v>3</v>
+      </c>
+      <c r="V26" s="4">
+        <v>2</v>
+      </c>
+      <c r="W26" s="4">
+        <v>1</v>
+      </c>
+      <c r="X26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="4"/>
+      <c r="AJ26" s="4"/>
+      <c r="AK26" s="4"/>
+      <c r="AL26" s="4"/>
+      <c r="AM26" s="4"/>
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="4"/>
+      <c r="AP26" s="4"/>
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A27" s="14">
+        <v>443</v>
+      </c>
+      <c r="B27" s="14">
+        <v>13263561</v>
+      </c>
+      <c r="C27" s="5">
+        <v>7426391</v>
+      </c>
+      <c r="D27" s="5" t="str">
+        <f>VLOOKUP(C27,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E27" s="14">
+        <v>43299316</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="3">
+        <v>48</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R27" s="4">
+        <v>1</v>
+      </c>
+      <c r="S27" s="4">
+        <v>2</v>
+      </c>
+      <c r="T27" s="4">
+        <v>3</v>
+      </c>
+      <c r="U27" s="4">
+        <v>3</v>
+      </c>
+      <c r="V27" s="4">
+        <v>2</v>
+      </c>
+      <c r="W27" s="4">
+        <v>1</v>
+      </c>
+      <c r="X27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="4"/>
+      <c r="AD27" s="4"/>
+      <c r="AE27" s="4"/>
+      <c r="AF27" s="4"/>
+      <c r="AG27" s="4"/>
+      <c r="AH27" s="4"/>
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
+      <c r="AL27" s="4"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="4"/>
+      <c r="AO27" s="4"/>
+      <c r="AP27" s="4"/>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <v>444</v>
+      </c>
+      <c r="B28" s="14">
+        <v>13263560</v>
+      </c>
+      <c r="C28" s="5">
+        <v>7426392</v>
+      </c>
+      <c r="D28" s="5" t="str">
+        <f>VLOOKUP(C28,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E28" s="14">
+        <v>43286101</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I28" s="13"/>
+      <c r="J28" s="3">
+        <v>48</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R28" s="4">
+        <v>1</v>
+      </c>
+      <c r="S28" s="4">
+        <v>2</v>
+      </c>
+      <c r="T28" s="4">
+        <v>3</v>
+      </c>
+      <c r="U28" s="4">
+        <v>3</v>
+      </c>
+      <c r="V28" s="4">
+        <v>2</v>
+      </c>
+      <c r="W28" s="4">
+        <v>1</v>
+      </c>
+      <c r="X28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA28" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="4"/>
+      <c r="AM28" s="4"/>
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="4"/>
+      <c r="AP28" s="4"/>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A29" s="14">
+        <v>445</v>
+      </c>
+      <c r="B29" s="14">
+        <v>13263491</v>
+      </c>
+      <c r="C29" s="5">
+        <v>5274753</v>
+      </c>
+      <c r="D29" s="5" t="str">
+        <f>VLOOKUP(C29,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E29" s="14">
+        <v>43409454</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="3">
+        <v>60</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="U29" s="4">
+        <v>1</v>
+      </c>
+      <c r="V29" s="4">
+        <v>2</v>
+      </c>
+      <c r="W29" s="4">
+        <v>3</v>
+      </c>
+      <c r="X29" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="4"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
+      <c r="AN29" s="4"/>
+      <c r="AO29" s="4"/>
+      <c r="AP29" s="4"/>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A30" s="14">
+        <v>446</v>
+      </c>
+      <c r="B30" s="14">
+        <v>13263493</v>
+      </c>
+      <c r="C30" s="5">
+        <v>5274761</v>
+      </c>
+      <c r="D30" s="5" t="str">
+        <f>VLOOKUP(C30,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E30" s="14">
+        <v>43772253</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="6">
+        <v>46178</v>
+      </c>
+      <c r="I30" s="13"/>
+      <c r="J30" s="3">
+        <v>36</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4">
+        <v>1</v>
+      </c>
+      <c r="O30" s="4">
+        <v>1</v>
+      </c>
+      <c r="P30" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>2</v>
+      </c>
+      <c r="R30" s="4">
+        <v>3</v>
+      </c>
+      <c r="S30" s="4">
+        <v>3</v>
+      </c>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
+      <c r="AM30" s="4"/>
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="4"/>
+      <c r="AP30" s="4"/>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A31" s="14">
+        <v>447</v>
+      </c>
+      <c r="B31" s="14">
+        <v>13263487</v>
+      </c>
+      <c r="C31" s="5">
+        <v>5274754</v>
+      </c>
+      <c r="D31" s="5" t="str">
+        <f>VLOOKUP(C31,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E31" s="14">
+        <v>43616206</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="6">
+        <v>46147</v>
+      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="3">
+        <v>48</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R31" s="4">
+        <v>1</v>
+      </c>
+      <c r="S31" s="4">
+        <v>2</v>
+      </c>
+      <c r="T31" s="4">
+        <v>3</v>
+      </c>
+      <c r="U31" s="4">
+        <v>3</v>
+      </c>
+      <c r="V31" s="4">
+        <v>2</v>
+      </c>
+      <c r="W31" s="4">
+        <v>1</v>
+      </c>
+      <c r="X31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB31" s="4"/>
+      <c r="AC31" s="4"/>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="4"/>
+      <c r="AP31" s="4"/>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A32" s="14">
+        <v>456</v>
+      </c>
+      <c r="B32" s="14">
+        <v>13172702</v>
+      </c>
+      <c r="C32" s="5">
+        <v>7268503</v>
+      </c>
+      <c r="D32" s="5" t="str">
+        <f>VLOOKUP(C32,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>VULTS</v>
+      </c>
+      <c r="E32" s="14">
+        <v>43299316</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H32" s="6">
+        <v>46172</v>
+      </c>
+      <c r="I32" s="13"/>
+      <c r="J32" s="3">
+        <v>84</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4">
+        <v>1</v>
+      </c>
+      <c r="S32" s="4">
+        <v>3</v>
+      </c>
+      <c r="T32" s="4">
+        <v>3</v>
+      </c>
+      <c r="U32" s="4">
+        <v>3</v>
+      </c>
+      <c r="V32" s="4">
+        <v>2</v>
+      </c>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="4"/>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="4"/>
+      <c r="AC32" s="4"/>
+      <c r="AD32" s="4"/>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
+      <c r="AM32" s="4"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4"/>
+      <c r="AP32" s="4"/>
+    </row>
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A33" s="14">
+        <v>467</v>
+      </c>
+      <c r="B33" s="14">
+        <v>13137448</v>
+      </c>
+      <c r="C33" s="5">
+        <v>5215309</v>
+      </c>
+      <c r="D33" s="5" t="str">
+        <f>VLOOKUP(C33,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E33" s="14">
+        <v>43263432</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="6">
+        <v>46113</v>
+      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="3">
+        <v>12</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4">
+        <v>1</v>
+      </c>
+      <c r="R33" s="4">
+        <v>2</v>
+      </c>
+      <c r="S33" s="4">
+        <v>3</v>
+      </c>
+      <c r="T33" s="4">
+        <v>3</v>
+      </c>
+      <c r="U33" s="4">
+        <v>2</v>
+      </c>
+      <c r="V33" s="4">
+        <v>1</v>
+      </c>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="4"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
+      <c r="AM33" s="4"/>
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="4"/>
+      <c r="AP33" s="4"/>
+    </row>
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A34" s="14">
+        <v>468</v>
+      </c>
+      <c r="B34" s="14">
+        <v>13249326</v>
+      </c>
+      <c r="C34" s="5">
+        <v>5269322</v>
+      </c>
+      <c r="D34" s="5" t="str">
+        <f>VLOOKUP(C34,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E34" s="14">
+        <v>43406455</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="6">
+        <v>46114</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="3">
+        <v>12</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4">
+        <v>1</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1</v>
+      </c>
+      <c r="P34" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>2</v>
+      </c>
+      <c r="R34" s="4">
+        <v>2</v>
+      </c>
+      <c r="S34" s="4">
+        <v>2</v>
+      </c>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="4"/>
+      <c r="AC34" s="4"/>
+      <c r="AD34" s="4"/>
+      <c r="AE34" s="4"/>
+      <c r="AF34" s="4"/>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
+      <c r="AL34" s="4"/>
+      <c r="AM34" s="4"/>
+      <c r="AN34" s="4"/>
+      <c r="AO34" s="4"/>
+      <c r="AP34" s="4"/>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A35" s="14">
+        <v>469</v>
+      </c>
+      <c r="B35" s="14">
+        <v>13249325</v>
+      </c>
+      <c r="C35" s="5">
+        <v>5269320</v>
+      </c>
+      <c r="D35" s="5" t="str">
+        <f>VLOOKUP(C35,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E35" s="14">
+        <v>43406455</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H35" s="6">
+        <v>46114</v>
+      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="3">
+        <v>12</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4">
+        <v>1</v>
+      </c>
+      <c r="O35" s="4">
+        <v>1</v>
+      </c>
+      <c r="P35" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>2</v>
+      </c>
+      <c r="R35" s="4">
+        <v>2</v>
+      </c>
+      <c r="S35" s="4">
+        <v>2</v>
+      </c>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="4"/>
+      <c r="AA35" s="4"/>
+      <c r="AB35" s="4"/>
+      <c r="AC35" s="4"/>
+      <c r="AD35" s="4"/>
+      <c r="AE35" s="4"/>
+      <c r="AF35" s="4"/>
+      <c r="AG35" s="4"/>
+      <c r="AH35" s="4"/>
+      <c r="AI35" s="4"/>
+      <c r="AJ35" s="4"/>
+      <c r="AK35" s="4"/>
+      <c r="AL35" s="4"/>
+      <c r="AM35" s="4"/>
+      <c r="AN35" s="4"/>
+      <c r="AO35" s="4"/>
+      <c r="AP35" s="4"/>
+    </row>
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>470</v>
+      </c>
+      <c r="B36" s="14">
+        <v>13137456</v>
+      </c>
+      <c r="C36" s="5">
+        <v>5215318</v>
+      </c>
+      <c r="D36" s="5" t="str">
+        <f>VLOOKUP(C36,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E36" s="14">
+        <v>43242437</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="6">
+        <v>46141</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="3">
+        <v>12</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4">
+        <v>1</v>
+      </c>
+      <c r="U36" s="4">
+        <v>1</v>
+      </c>
+      <c r="V36" s="4">
+        <v>2</v>
+      </c>
+      <c r="W36" s="4">
+        <v>2</v>
+      </c>
+      <c r="X36" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z36" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="4"/>
+      <c r="AC36" s="4"/>
+      <c r="AD36" s="4"/>
+      <c r="AE36" s="4"/>
+      <c r="AF36" s="4"/>
+      <c r="AG36" s="4"/>
+      <c r="AH36" s="4"/>
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4"/>
+      <c r="AK36" s="4"/>
+      <c r="AL36" s="4"/>
+      <c r="AM36" s="4"/>
+      <c r="AN36" s="4"/>
+      <c r="AO36" s="4"/>
+      <c r="AP36" s="4"/>
+    </row>
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A37" s="14">
+        <v>471</v>
+      </c>
+      <c r="B37" s="14">
+        <v>13137556</v>
+      </c>
+      <c r="C37" s="5">
+        <v>5215319</v>
+      </c>
+      <c r="D37" s="5" t="str">
+        <f>VLOOKUP(C37,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E37" s="14">
+        <v>43242437</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="6">
+        <v>46141</v>
+      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="3">
+        <v>12</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4">
+        <v>1</v>
+      </c>
+      <c r="U37" s="4">
+        <v>1</v>
+      </c>
+      <c r="V37" s="4">
+        <v>2</v>
+      </c>
+      <c r="W37" s="4">
+        <v>2</v>
+      </c>
+      <c r="X37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y37" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="4">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="4"/>
+      <c r="AC37" s="4"/>
+      <c r="AD37" s="4"/>
+      <c r="AE37" s="4"/>
+      <c r="AF37" s="4"/>
+      <c r="AG37" s="4"/>
+      <c r="AH37" s="4"/>
+      <c r="AI37" s="4"/>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
+      <c r="AL37" s="4"/>
+      <c r="AM37" s="4"/>
+      <c r="AN37" s="4"/>
+      <c r="AO37" s="4"/>
+      <c r="AP37" s="4"/>
+    </row>
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A38" s="14">
+        <v>472</v>
+      </c>
+      <c r="B38" s="14">
+        <v>13249317</v>
+      </c>
+      <c r="C38" s="5">
+        <v>5269321</v>
+      </c>
+      <c r="D38" s="5" t="str">
+        <f>VLOOKUP(C38,[1]Planilha2!$D$1:$E$65536,2,0)</f>
+        <v>AZABA</v>
+      </c>
+      <c r="E38" s="14">
+        <v>43406455</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" s="15">
+        <v>46114</v>
+      </c>
+      <c r="I38" s="13"/>
+      <c r="J38" s="3">
+        <v>10</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4">
+        <v>1</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1</v>
+      </c>
+      <c r="P38" s="4">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>2</v>
+      </c>
+      <c r="R38" s="4">
+        <v>2</v>
+      </c>
+      <c r="S38" s="4">
+        <v>2</v>
+      </c>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AC38" s="4"/>
+      <c r="AD38" s="4"/>
+      <c r="AE38" s="4"/>
+      <c r="AF38" s="4"/>
+      <c r="AG38" s="4"/>
+      <c r="AH38" s="4"/>
+      <c r="AI38" s="4"/>
+      <c r="AJ38" s="4"/>
+      <c r="AK38" s="4"/>
+      <c r="AL38" s="4"/>
+      <c r="AM38" s="4"/>
+      <c r="AN38" s="4"/>
+      <c r="AO38" s="4"/>
+      <c r="AP38" s="4"/>
+    </row>
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C39" s="12"/>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C40" s="12"/>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C41" s="12"/>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C42" s="12"/>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C43" s="12"/>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C44" s="12"/>
     </row>
   </sheetData>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7ABED0-A763-4210-9DF5-44CAEBF09BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3311190-9D98-4BEC-9798-FC0185D80DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d52965f3075d7c0/Documentos/GitHub/Catalogo-Olympikus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ED6542-5A1E-4B42-B404-31131A61440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{87ED6542-5A1E-4B42-B404-31131A61440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BCBA85-7209-48B3-B231-A211E50C2063}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
   <sheets>
     <sheet name="DISPO" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="105">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>VULTS</t>
+  </si>
+  <si>
+    <t>SIM</t>
   </si>
 </sst>
 </file>
@@ -534,7 +537,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -543,7 +546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -904,26 +907,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
   <dimension ref="A1:AP30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="1"/>
-    <col min="8" max="8" width="12.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="22" width="3.42578125" customWidth="1"/>
-    <col min="23" max="23" width="4.42578125" customWidth="1"/>
-    <col min="24" max="24" width="5.140625" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" customWidth="1"/>
-    <col min="27" max="27" width="4.5703125" customWidth="1"/>
-    <col min="28" max="42" width="6.140625" customWidth="1"/>
+    <col min="3" max="4" width="8.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" style="1"/>
+    <col min="8" max="8" width="12.54296875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="3.453125" customWidth="1"/>
+    <col min="23" max="23" width="4.453125" customWidth="1"/>
+    <col min="24" max="24" width="5.1796875" customWidth="1"/>
+    <col min="25" max="26" width="4.81640625" customWidth="1"/>
+    <col min="27" max="27" width="4.54296875" customWidth="1"/>
+    <col min="28" max="42" width="6.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>69</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>57</v>
       </c>
@@ -1129,7 +1132,7 @@
       <c r="AO2" s="4"/>
       <c r="AP2" s="4"/>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>314</v>
       </c>
@@ -1205,7 +1208,7 @@
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>322</v>
       </c>
@@ -1289,7 +1292,7 @@
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>323</v>
       </c>
@@ -1373,7 +1376,7 @@
       <c r="AO5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>325</v>
       </c>
@@ -1449,7 +1452,7 @@
       <c r="AO6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>80</v>
       </c>
@@ -1519,7 +1522,7 @@
       <c r="AO7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>334</v>
       </c>
@@ -1595,7 +1598,7 @@
       <c r="AO8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>335</v>
       </c>
@@ -1671,7 +1674,7 @@
       <c r="AO9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>336</v>
       </c>
@@ -1747,7 +1750,7 @@
       <c r="AO10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>339</v>
       </c>
@@ -1821,7 +1824,7 @@
       <c r="AO11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>340</v>
       </c>
@@ -1897,7 +1900,7 @@
       <c r="AO12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>341</v>
       </c>
@@ -1971,7 +1974,7 @@
       <c r="AO13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>388</v>
       </c>
@@ -2033,7 +2036,7 @@
       <c r="AO14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>390</v>
       </c>
@@ -2105,7 +2108,7 @@
       <c r="AO15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>409</v>
       </c>
@@ -2177,7 +2180,7 @@
       <c r="AO16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>412</v>
       </c>
@@ -2249,7 +2252,7 @@
       <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>426</v>
       </c>
@@ -2335,7 +2338,7 @@
       <c r="AO18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>427</v>
       </c>
@@ -2421,7 +2424,7 @@
       <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>429</v>
       </c>
@@ -2507,7 +2510,7 @@
       <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>436</v>
       </c>
@@ -2593,7 +2596,7 @@
       <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>441</v>
       </c>
@@ -2679,7 +2682,7 @@
       <c r="AO22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A23" s="14">
         <v>442</v>
       </c>
@@ -2765,7 +2768,7 @@
       <c r="AO23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A24" s="14">
         <v>443</v>
       </c>
@@ -2851,7 +2854,7 @@
       <c r="AO24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A25" s="14">
         <v>446</v>
       </c>
@@ -2876,7 +2879,9 @@
       <c r="H25" s="6">
         <v>46178</v>
       </c>
-      <c r="I25" s="13"/>
+      <c r="I25" s="13" t="s">
+        <v>104</v>
+      </c>
       <c r="J25" s="3">
         <v>36</v>
       </c>
@@ -2925,7 +2930,7 @@
       <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
       <c r="A26" s="14">
         <v>447</v>
       </c>
@@ -3011,16 +3016,16 @@
       <c r="AO26" s="4"/>
       <c r="AP26" s="4"/>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
       <c r="C27" s="12"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
       <c r="C28" s="12"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
       <c r="C29" s="12"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
       <c r="C30" s="12"/>
     </row>
   </sheetData>
@@ -3039,13 +3044,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FFEE10-842F-42AA-BEA5-1A4CC019264C}">
   <dimension ref="D2:F36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -3056,7 +3061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
         <v>1</v>
       </c>
@@ -3067,7 +3072,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
         <v>2</v>
       </c>
@@ -3078,7 +3083,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D5" t="s">
         <v>3</v>
       </c>
@@ -3089,7 +3094,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -3097,7 +3102,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
         <v>5</v>
       </c>
@@ -3105,147 +3110,147 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:6" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D36" t="s">
         <v>34</v>
       </c>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ED6542-5A1E-4B42-B404-31131A61440F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EBA6EE-6B7A-4240-89BD-AB5E3122D12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7d52965f3075d7c0/Documentos/GitHub/Catalogo-Olympikus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{47EBA6EE-6B7A-4240-89BD-AB5E3122D12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{547BDB98-8079-4571-B703-5C584B2028BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1420BC-26F3-4D3E-9D1A-5477021E94FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
   <sheets>
     <sheet name="DISPO" sheetId="3" r:id="rId1"/>
@@ -431,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,6 +459,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -505,7 +511,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -556,6 +562,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -915,27 +924,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.81640625" style="1"/>
-    <col min="8" max="8" width="12.54296875" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="22" width="3.453125" customWidth="1"/>
-    <col min="23" max="23" width="4.453125" customWidth="1"/>
-    <col min="24" max="24" width="5.1796875" customWidth="1"/>
-    <col min="25" max="26" width="4.81640625" customWidth="1"/>
-    <col min="27" max="27" width="4.54296875" customWidth="1"/>
-    <col min="28" max="42" width="6.1796875" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="12.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="22" width="3.42578125" customWidth="1"/>
+    <col min="23" max="23" width="4.42578125" customWidth="1"/>
+    <col min="24" max="24" width="5.140625" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" customWidth="1"/>
+    <col min="27" max="27" width="4.5703125" customWidth="1"/>
+    <col min="28" max="42" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>69</v>
       </c>
@@ -1063,7 +1073,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>57</v>
       </c>
@@ -1141,7 +1151,7 @@
       <c r="AO2" s="4"/>
       <c r="AP2" s="4"/>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>314</v>
       </c>
@@ -1217,7 +1227,7 @@
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>322</v>
       </c>
@@ -1301,7 +1311,7 @@
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>323</v>
       </c>
@@ -1385,7 +1395,7 @@
       <c r="AO5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>325</v>
       </c>
@@ -1461,7 +1471,7 @@
       <c r="AO6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>80</v>
       </c>
@@ -1531,7 +1541,7 @@
       <c r="AO7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>334</v>
       </c>
@@ -1607,7 +1617,7 @@
       <c r="AO8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>335</v>
       </c>
@@ -1683,7 +1693,7 @@
       <c r="AO9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>336</v>
       </c>
@@ -1759,7 +1769,7 @@
       <c r="AO10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>339</v>
       </c>
@@ -1833,7 +1843,7 @@
       <c r="AO11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>340</v>
       </c>
@@ -1909,7 +1919,7 @@
       <c r="AO12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>341</v>
       </c>
@@ -1983,7 +1993,7 @@
       <c r="AO13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>388</v>
       </c>
@@ -2045,7 +2055,7 @@
       <c r="AO14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>390</v>
       </c>
@@ -2117,7 +2127,7 @@
       <c r="AO15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>409</v>
       </c>
@@ -2189,7 +2199,7 @@
       <c r="AO16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>412</v>
       </c>
@@ -2261,15 +2271,15 @@
       <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>426</v>
       </c>
       <c r="B18" s="14">
         <v>13263499</v>
       </c>
-      <c r="C18" s="5">
-        <v>5274744</v>
+      <c r="C18" s="18">
+        <v>5274745</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>102</v>
@@ -2347,7 +2357,7 @@
       <c r="AO18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>427</v>
       </c>
@@ -2433,7 +2443,7 @@
       <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>429</v>
       </c>
@@ -2519,7 +2529,7 @@
       <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>436</v>
       </c>
@@ -2605,7 +2615,7 @@
       <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>441</v>
       </c>
@@ -2691,7 +2701,7 @@
       <c r="AO22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>442</v>
       </c>
@@ -2777,7 +2787,7 @@
       <c r="AO23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>443</v>
       </c>
@@ -2863,7 +2873,7 @@
       <c r="AO24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>446</v>
       </c>
@@ -2937,7 +2947,7 @@
       <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>447</v>
       </c>
@@ -3023,20 +3033,26 @@
       <c r="AO26" s="4"/>
       <c r="AP26" s="4"/>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C27" s="12"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C28" s="12"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C29" s="12"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C30" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
+  <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="5274744"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>
@@ -3051,13 +3067,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FFEE10-842F-42AA-BEA5-1A4CC019264C}">
   <dimension ref="D2:F36"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -3068,7 +3084,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>1</v>
       </c>
@@ -3079,7 +3095,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>2</v>
       </c>
@@ -3090,7 +3106,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>3</v>
       </c>
@@ -3101,7 +3117,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -3109,7 +3125,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>5</v>
       </c>
@@ -3117,147 +3133,147 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="4:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D27" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
         <v>34</v>
       </c>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FBF264-DE53-4081-89A1-21F48B77EDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E7B8C8-DA9F-4A26-AFFA-E89D725AE504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -2276,10 +2276,10 @@
         <v>426</v>
       </c>
       <c r="B18" s="14">
-        <v>13263498</v>
+        <v>13263497</v>
       </c>
       <c r="C18" s="18">
-        <v>5274745</v>
+        <v>5274744</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>102</v>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E7B8C8-DA9F-4A26-AFFA-E89D725AE504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B5104A-400C-4641-A4B2-15D701230DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -1227,7 +1227,7 @@
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>322</v>
       </c>
@@ -1311,7 +1311,7 @@
       <c r="AO4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>323</v>
       </c>
@@ -2271,7 +2271,7 @@
       <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>426</v>
       </c>
@@ -2357,15 +2357,15 @@
       <c r="AO18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>427</v>
       </c>
       <c r="B19" s="16">
-        <v>12265543</v>
+        <v>12265544</v>
       </c>
       <c r="C19" s="17">
-        <v>5348674</v>
+        <v>5348675</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>103</v>
@@ -3047,9 +3047,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-    <filterColumn colId="1">
+    <filterColumn colId="4">
       <filters>
-        <filter val="5274744"/>
+        <filter val="RUSH"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B5104A-400C-4641-A4B2-15D701230DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7417FD28-1286-4CA7-AC76-DD6BA06897CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -924,7 +924,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AP30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1073,7 +1072,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>57</v>
       </c>
@@ -1151,7 +1150,7 @@
       <c r="AO2" s="4"/>
       <c r="AP2" s="4"/>
     </row>
-    <row r="3" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>314</v>
       </c>
@@ -1395,7 +1394,7 @@
       <c r="AO5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>325</v>
       </c>
@@ -1471,7 +1470,7 @@
       <c r="AO6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>80</v>
       </c>
@@ -1541,7 +1540,7 @@
       <c r="AO7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>334</v>
       </c>
@@ -1617,7 +1616,7 @@
       <c r="AO8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>335</v>
       </c>
@@ -1693,7 +1692,7 @@
       <c r="AO9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>336</v>
       </c>
@@ -1769,7 +1768,7 @@
       <c r="AO10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>339</v>
       </c>
@@ -1843,7 +1842,7 @@
       <c r="AO11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>340</v>
       </c>
@@ -1919,7 +1918,7 @@
       <c r="AO12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>341</v>
       </c>
@@ -1993,7 +1992,7 @@
       <c r="AO13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>388</v>
       </c>
@@ -2055,7 +2054,7 @@
       <c r="AO14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>390</v>
       </c>
@@ -2127,7 +2126,7 @@
       <c r="AO15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>409</v>
       </c>
@@ -2199,7 +2198,7 @@
       <c r="AO16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>412</v>
       </c>
@@ -2271,7 +2270,7 @@
       <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>426</v>
       </c>
@@ -2443,7 +2442,7 @@
       <c r="AO19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>429</v>
       </c>
@@ -2529,7 +2528,7 @@
       <c r="AO20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>436</v>
       </c>
@@ -2615,7 +2614,7 @@
       <c r="AO21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>441</v>
       </c>
@@ -2701,7 +2700,7 @@
       <c r="AO22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>442</v>
       </c>
@@ -2787,7 +2786,7 @@
       <c r="AO23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>443</v>
       </c>
@@ -2873,7 +2872,7 @@
       <c r="AO24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>446</v>
       </c>
@@ -2947,7 +2946,7 @@
       <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>447</v>
       </c>
@@ -3046,13 +3045,7 @@
       <c r="C30" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="RUSH"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="1" priority="107"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4250A88F-8C9D-4B20-A2C9-12D4EAB86D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300C0672-1416-4AF0-B213-79BF21725C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -162,9 +162,6 @@
     <t>COR</t>
   </si>
   <si>
-    <t>DATA ENTREGA</t>
-  </si>
-  <si>
     <t>SALDO</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>VULTS</t>
+  </si>
+  <si>
+    <t>PREV. FAT.</t>
   </si>
 </sst>
 </file>
@@ -941,7 +941,7 @@
   <sheetData>
     <row r="1" spans="1:42" s="11" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>37</v>
@@ -950,25 +950,25 @@
         <v>38</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>39</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="K1" s="9">
         <v>28</v>
@@ -1022,49 +1022,49 @@
         <v>44</v>
       </c>
       <c r="AB1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AD1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AG1" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AH1" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="AH1" s="9" t="s">
-        <v>58</v>
-      </c>
       <c r="AI1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AK1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AL1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AM1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AN1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="AN1" s="9" t="s">
+      <c r="AO1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AP1" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="AP1" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
@@ -1078,16 +1078,16 @@
         <v>5274741</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" s="5">
         <v>43752263</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="H2" s="6">
         <v>46147</v>
@@ -1156,16 +1156,16 @@
         <v>5013428</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E3" s="5">
         <v>43632407</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="H3" s="6">
         <v>46172</v>
@@ -1232,16 +1232,16 @@
         <v>7372755</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E4" s="5">
         <v>43667419</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H4" s="6">
         <v>46162</v>
@@ -1257,19 +1257,19 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V4" s="4">
         <v>1</v>
@@ -1316,16 +1316,16 @@
         <v>7372771</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" s="5">
         <v>43667419</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5" s="6">
         <v>46193</v>
@@ -1341,7 +1341,7 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R5" s="4">
         <v>2</v>
@@ -1356,22 +1356,22 @@
         <v>3</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1400,16 +1400,16 @@
         <v>5199180</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="5">
         <v>43395156</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H6" s="6">
         <v>46165</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" s="14">
         <v>12837174</v>
@@ -1476,16 +1476,16 @@
         <v>5038292</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" s="14">
         <v>54104269</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H7" s="6">
         <v>46158</v>
@@ -1546,16 +1546,16 @@
         <v>6913394</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" s="14">
         <v>43927547</v>
       </c>
       <c r="F8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>82</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>83</v>
       </c>
       <c r="H8" s="6">
         <v>46147</v>
@@ -1622,16 +1622,16 @@
         <v>7228507</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" s="14">
         <v>43299316</v>
       </c>
       <c r="F9" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>85</v>
       </c>
       <c r="H9" s="6">
         <v>46147</v>
@@ -1696,16 +1696,16 @@
         <v>4993104</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="14">
         <v>43389459</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H10" s="6">
         <v>46147</v>
@@ -1758,16 +1758,16 @@
         <v>4993255</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" s="14">
         <v>43632407</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="6">
         <v>46172</v>
@@ -1830,16 +1830,16 @@
         <v>4993370</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" s="14">
         <v>43393460</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H12" s="6">
         <v>46172</v>
@@ -1902,16 +1902,16 @@
         <v>4993371</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E13" s="14">
         <v>43393460</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13" s="6">
         <v>46172</v>
@@ -1974,16 +1974,16 @@
         <v>5274744</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E14" s="14">
         <v>43395156</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H14" s="6">
         <v>46147</v>
@@ -1998,19 +1998,19 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U14" s="4">
         <v>1</v>
@@ -2031,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="AA14" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
@@ -2060,16 +2060,16 @@
         <v>7426389</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E15" s="14">
         <v>43667419</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H15" s="6">
         <v>46147</v>
@@ -2084,10 +2084,10 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R15" s="4">
         <v>1</v>
@@ -2108,16 +2108,16 @@
         <v>1</v>
       </c>
       <c r="X15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA15" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
@@ -2146,16 +2146,16 @@
         <v>5274747</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16" s="14">
         <v>43616206</v>
       </c>
       <c r="F16" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>91</v>
       </c>
       <c r="H16" s="6">
         <v>46147</v>
@@ -2170,10 +2170,10 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R16" s="4">
         <v>1</v>
@@ -2194,16 +2194,16 @@
         <v>1</v>
       </c>
       <c r="X16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA16" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
@@ -2232,16 +2232,16 @@
         <v>7426398</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" s="14">
         <v>43927547</v>
       </c>
       <c r="F17" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>92</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>93</v>
       </c>
       <c r="H17" s="6">
         <v>46178</v>
@@ -2256,10 +2256,10 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R17" s="4">
         <v>1</v>
@@ -2280,16 +2280,16 @@
         <v>1</v>
       </c>
       <c r="X17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA17" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
@@ -2318,16 +2318,16 @@
         <v>7426399</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E18" s="14">
         <v>43299316</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H18" s="6">
         <v>46178</v>
@@ -2342,10 +2342,10 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R18" s="4">
         <v>1</v>
@@ -2366,16 +2366,16 @@
         <v>1</v>
       </c>
       <c r="X18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA18" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2404,16 +2404,16 @@
         <v>5274759</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" s="14">
         <v>43263432</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H19" s="6">
         <v>46178</v>
@@ -2428,10 +2428,10 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R19" s="4">
         <v>1</v>
@@ -2452,16 +2452,16 @@
         <v>1</v>
       </c>
       <c r="X19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -2490,16 +2490,16 @@
         <v>7426391</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E20" s="14">
         <v>43299316</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="6">
         <v>46147</v>
@@ -2514,10 +2514,10 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R20" s="4">
         <v>1</v>
@@ -2538,16 +2538,16 @@
         <v>1</v>
       </c>
       <c r="X20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA20" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -2576,16 +2576,16 @@
         <v>5274761</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21" s="14">
         <v>43772253</v>
       </c>
       <c r="F21" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>96</v>
       </c>
       <c r="H21" s="6">
         <v>46178</v>
@@ -2650,16 +2650,16 @@
         <v>5274754</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" s="14">
         <v>43616206</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" s="6">
         <v>46147</v>
@@ -2674,10 +2674,10 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R22" s="4">
         <v>1</v>
@@ -2698,16 +2698,16 @@
         <v>1</v>
       </c>
       <c r="X22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA22" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
@@ -2736,16 +2736,16 @@
         <v>5240742</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" s="14">
         <v>43342471</v>
       </c>
       <c r="F23" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="H23" s="6">
         <v>46113</v>
@@ -2810,16 +2810,16 @@
         <v>5240741</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="14">
         <v>43342471</v>
       </c>
       <c r="F24" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="H24" s="6">
         <v>46113</v>
@@ -2884,16 +2884,16 @@
         <v>5240740</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" s="14">
         <v>43342471</v>
       </c>
       <c r="F25" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="H25" s="6">
         <v>46113</v>
@@ -2958,16 +2958,16 @@
         <v>5245130</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E26" s="14">
         <v>43342471</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6">
         <v>46132</v>
@@ -3132,7 +3132,7 @@
         <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="4:6" x14ac:dyDescent="0.25">
@@ -3140,10 +3140,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="4:6" x14ac:dyDescent="0.25">
@@ -3154,7 +3154,7 @@
         <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="4:6" x14ac:dyDescent="0.25">
@@ -3162,10 +3162,10 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="4:6" x14ac:dyDescent="0.25">
@@ -3173,7 +3173,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="4:6" x14ac:dyDescent="0.25">
@@ -3181,7 +3181,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="4:6" x14ac:dyDescent="0.25">

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2695DA8E-1F12-4C5D-8E20-B54149497DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4188BA-B77C-4A0D-80C9-5013242D1E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="104">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -505,7 +505,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -539,9 +539,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -918,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AP53"/>
+  <dimension ref="A1:AP52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
@@ -928,7 +925,7 @@
     <col min="5" max="5" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" style="1"/>
-    <col min="8" max="8" width="12.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="22" width="3.42578125" customWidth="1"/>
@@ -1092,7 +1089,7 @@
       <c r="H2" s="6">
         <v>46147</v>
       </c>
-      <c r="I2" s="13"/>
+      <c r="I2" s="12"/>
       <c r="J2" s="3">
         <v>24</v>
       </c>
@@ -1170,7 +1167,7 @@
       <c r="H3" s="6">
         <v>46172</v>
       </c>
-      <c r="I3" s="13"/>
+      <c r="I3" s="12"/>
       <c r="J3" s="3">
         <v>24</v>
       </c>
@@ -1246,7 +1243,7 @@
       <c r="H4" s="6">
         <v>46162</v>
       </c>
-      <c r="I4" s="13"/>
+      <c r="I4" s="12"/>
       <c r="J4" s="3">
         <v>24</v>
       </c>
@@ -1330,7 +1327,7 @@
       <c r="H5" s="6">
         <v>46193</v>
       </c>
-      <c r="I5" s="13"/>
+      <c r="I5" s="12"/>
       <c r="J5" s="3">
         <v>48</v>
       </c>
@@ -1414,7 +1411,7 @@
       <c r="H6" s="6">
         <v>46165</v>
       </c>
-      <c r="I6" s="13"/>
+      <c r="I6" s="12"/>
       <c r="J6" s="3">
         <v>228</v>
       </c>
@@ -1466,10 +1463,10 @@
       <c r="AP6" s="4"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>12837174</v>
       </c>
       <c r="C7" s="5">
@@ -1478,19 +1475,19 @@
       <c r="D7" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>54104269</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>75</v>
       </c>
       <c r="H7" s="6">
         <v>46158</v>
       </c>
-      <c r="I7" s="13"/>
+      <c r="I7" s="12"/>
       <c r="J7" s="3">
         <v>48</v>
       </c>
@@ -1536,10 +1533,10 @@
       <c r="AP7" s="4"/>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="13">
         <v>336</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>12757541</v>
       </c>
       <c r="C8" s="5">
@@ -1548,19 +1545,19 @@
       <c r="D8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>43927547</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>82</v>
       </c>
       <c r="H8" s="6">
         <v>46147</v>
       </c>
-      <c r="I8" s="13"/>
+      <c r="I8" s="12"/>
       <c r="J8" s="3">
         <v>36</v>
       </c>
@@ -1612,10 +1609,10 @@
       <c r="AP8" s="4"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="13">
         <v>341</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>13140161</v>
       </c>
       <c r="C9" s="5">
@@ -1624,19 +1621,19 @@
       <c r="D9" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>43299316</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="13" t="s">
         <v>84</v>
       </c>
       <c r="H9" s="6">
         <v>46147</v>
       </c>
-      <c r="I9" s="13"/>
+      <c r="I9" s="12"/>
       <c r="J9" s="3">
         <v>108</v>
       </c>
@@ -1686,10 +1683,10 @@
       <c r="AP9" s="4"/>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="13">
         <v>388</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>12757545</v>
       </c>
       <c r="C10" s="5">
@@ -1698,19 +1695,19 @@
       <c r="D10" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <v>43389459</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>49</v>
       </c>
       <c r="H10" s="6">
         <v>46147</v>
       </c>
-      <c r="I10" s="13"/>
+      <c r="I10" s="12"/>
       <c r="J10" s="3">
         <v>60</v>
       </c>
@@ -1748,10 +1745,10 @@
       <c r="AP10" s="4"/>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="13">
         <v>390</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>12757893</v>
       </c>
       <c r="C11" s="5">
@@ -1760,19 +1757,19 @@
       <c r="D11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <v>43632407</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>50</v>
       </c>
       <c r="H11" s="6">
         <v>46172</v>
       </c>
-      <c r="I11" s="13"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="3">
         <v>48</v>
       </c>
@@ -1820,10 +1817,10 @@
       <c r="AP11" s="4"/>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A12" s="14">
+      <c r="A12" s="13">
         <v>409</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <v>12758052</v>
       </c>
       <c r="C12" s="5">
@@ -1832,19 +1829,19 @@
       <c r="D12" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <v>43393460</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>75</v>
       </c>
       <c r="H12" s="6">
         <v>46172</v>
       </c>
-      <c r="I12" s="13"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="3">
         <v>12</v>
       </c>
@@ -1892,10 +1889,10 @@
       <c r="AP12" s="4"/>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A13" s="14">
+      <c r="A13" s="13">
         <v>412</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>12758063</v>
       </c>
       <c r="C13" s="5">
@@ -1904,19 +1901,19 @@
       <c r="D13" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="13">
         <v>43393460</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="13" t="s">
         <v>75</v>
       </c>
       <c r="H13" s="6">
         <v>46172</v>
       </c>
-      <c r="I13" s="13"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="3">
         <v>12</v>
       </c>
@@ -1964,10 +1961,10 @@
       <c r="AP13" s="4"/>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A14" s="14">
+      <c r="A14" s="13">
         <v>426</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>13263499</v>
       </c>
       <c r="C14" s="5">
@@ -1976,19 +1973,19 @@
       <c r="D14" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>43395156</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>87</v>
       </c>
       <c r="H14" s="6">
         <v>46147</v>
       </c>
-      <c r="I14" s="13"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="3">
         <v>108</v>
       </c>
@@ -2050,10 +2047,10 @@
       <c r="AP14" s="4"/>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A15" s="14">
+      <c r="A15" s="13">
         <v>427</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <v>13263552</v>
       </c>
       <c r="C15" s="5">
@@ -2062,19 +2059,19 @@
       <c r="D15" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>43667419</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>88</v>
       </c>
       <c r="H15" s="6">
         <v>46147</v>
       </c>
-      <c r="I15" s="13"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="3">
         <v>36</v>
       </c>
@@ -2136,10 +2133,10 @@
       <c r="AP15" s="4"/>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
+      <c r="A16" s="13">
         <v>429</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>13263489</v>
       </c>
       <c r="C16" s="5">
@@ -2148,19 +2145,19 @@
       <c r="D16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="13">
         <v>43616206</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="13" t="s">
         <v>90</v>
       </c>
       <c r="H16" s="6">
         <v>46147</v>
       </c>
-      <c r="I16" s="13"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="3">
         <v>48</v>
       </c>
@@ -2222,10 +2219,10 @@
       <c r="AP16" s="4"/>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+      <c r="A17" s="13">
         <v>436</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <v>13263547</v>
       </c>
       <c r="C17" s="5">
@@ -2234,19 +2231,19 @@
       <c r="D17" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="13">
         <v>43927547</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="13" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="6">
         <v>46178</v>
       </c>
-      <c r="I17" s="13"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="3">
         <v>48</v>
       </c>
@@ -2308,10 +2305,10 @@
       <c r="AP17" s="4"/>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+      <c r="A18" s="13">
         <v>441</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="13">
         <v>13263549</v>
       </c>
       <c r="C18" s="5">
@@ -2320,19 +2317,19 @@
       <c r="D18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="13">
         <v>43299316</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="13" t="s">
         <v>75</v>
       </c>
       <c r="H18" s="6">
         <v>46178</v>
       </c>
-      <c r="I18" s="13"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="3">
         <v>60</v>
       </c>
@@ -2394,31 +2391,31 @@
       <c r="AP18" s="4"/>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
+      <c r="A19" s="13">
         <v>442</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="15">
         <v>13263498</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>5274759</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>43263432</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="13" t="s">
         <v>93</v>
       </c>
       <c r="H19" s="6">
         <v>46178</v>
       </c>
-      <c r="I19" s="13"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="3">
         <v>36</v>
       </c>
@@ -2480,10 +2477,10 @@
       <c r="AP19" s="4"/>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+      <c r="A20" s="13">
         <v>443</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <v>13263561</v>
       </c>
       <c r="C20" s="5">
@@ -2492,19 +2489,19 @@
       <c r="D20" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="13">
         <v>43299316</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="13" t="s">
         <v>75</v>
       </c>
       <c r="H20" s="6">
         <v>46147</v>
       </c>
-      <c r="I20" s="13"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="3">
         <v>48</v>
       </c>
@@ -2566,10 +2563,10 @@
       <c r="AP20" s="4"/>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+      <c r="A21" s="13">
         <v>446</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <v>13263493</v>
       </c>
       <c r="C21" s="5">
@@ -2578,19 +2575,19 @@
       <c r="D21" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="13">
         <v>43772253</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>95</v>
       </c>
       <c r="H21" s="6">
         <v>46178</v>
       </c>
-      <c r="I21" s="13"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="3">
         <v>36</v>
       </c>
@@ -2640,10 +2637,10 @@
       <c r="AP21" s="4"/>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+      <c r="A22" s="13">
         <v>447</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="13">
         <v>13263487</v>
       </c>
       <c r="C22" s="5">
@@ -2652,19 +2649,19 @@
       <c r="D22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="13">
         <v>43616206</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="13" t="s">
         <v>96</v>
       </c>
       <c r="H22" s="6">
         <v>46147</v>
       </c>
-      <c r="I22" s="13"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="3">
         <v>48</v>
       </c>
@@ -2726,10 +2723,10 @@
       <c r="AP22" s="4"/>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A23" s="14">
+      <c r="A23" s="13">
         <v>483</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="13">
         <v>13175375</v>
       </c>
       <c r="C23" s="5">
@@ -2738,19 +2735,19 @@
       <c r="D23" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="13">
         <v>43342471</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="13" t="s">
         <v>99</v>
       </c>
       <c r="H23" s="6">
         <v>46113</v>
       </c>
-      <c r="I23" s="13"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="3">
         <v>156</v>
       </c>
@@ -2800,10 +2797,10 @@
       <c r="AP23" s="4"/>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A24" s="14">
+      <c r="A24" s="13">
         <v>484</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="13">
         <v>13175377</v>
       </c>
       <c r="C24" s="5">
@@ -2812,19 +2809,19 @@
       <c r="D24" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="13">
         <v>43342471</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="13" t="s">
         <v>99</v>
       </c>
       <c r="H24" s="6">
         <v>46113</v>
       </c>
-      <c r="I24" s="13"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="3">
         <v>192</v>
       </c>
@@ -2874,10 +2871,10 @@
       <c r="AP24" s="4"/>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A25" s="14">
+      <c r="A25" s="13">
         <v>485</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="13">
         <v>13175378</v>
       </c>
       <c r="C25" s="5">
@@ -2886,19 +2883,19 @@
       <c r="D25" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="13">
         <v>43342471</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="13" t="s">
         <v>99</v>
       </c>
       <c r="H25" s="6">
         <v>46113</v>
       </c>
-      <c r="I25" s="13"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="3">
         <v>360</v>
       </c>
@@ -2948,10 +2945,10 @@
       <c r="AP25" s="4"/>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <v>486</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="13">
         <v>13185973</v>
       </c>
       <c r="C26" s="5">
@@ -2960,19 +2957,19 @@
       <c r="D26" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="13">
         <v>43342471</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="13" t="s">
         <v>100</v>
       </c>
       <c r="H26" s="6">
         <v>46132</v>
       </c>
-      <c r="I26" s="13"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="3">
         <v>108</v>
       </c>
@@ -3022,85 +3019,165 @@
       <c r="AP26" s="4"/>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C27" s="12"/>
+      <c r="A27" s="13">
+        <v>4422</v>
+      </c>
+      <c r="B27" s="15">
+        <v>13263499</v>
+      </c>
+      <c r="C27" s="16">
+        <v>5274757</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27" s="13">
+        <v>43263432</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="6">
+        <v>46178</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="J27" s="3">
+        <v>36</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="R27" s="4">
+        <v>1</v>
+      </c>
+      <c r="S27" s="4">
+        <v>3</v>
+      </c>
+      <c r="T27" s="4">
+        <v>2</v>
+      </c>
+      <c r="U27" s="4">
+        <v>3</v>
+      </c>
+      <c r="V27" s="4">
+        <v>2</v>
+      </c>
+      <c r="W27" s="4">
+        <v>1</v>
+      </c>
+      <c r="X27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA27" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB27" s="4"/>
+      <c r="AC27" s="4"/>
+      <c r="AD27" s="4"/>
+      <c r="AE27" s="4"/>
+      <c r="AF27" s="4"/>
+      <c r="AG27" s="4"/>
+      <c r="AH27" s="4"/>
+      <c r="AI27" s="4"/>
+      <c r="AJ27" s="4"/>
+      <c r="AK27" s="4"/>
+      <c r="AL27" s="4"/>
+      <c r="AM27" s="4"/>
+      <c r="AN27" s="4"/>
+      <c r="AO27" s="4"/>
+      <c r="AP27" s="4"/>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C28" s="12"/>
+      <c r="C28" s="17"/>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C29" s="18"/>
+      <c r="C29" s="17"/>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C30" s="18"/>
+      <c r="C30" s="17"/>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C31" s="18"/>
+      <c r="C31" s="17"/>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="C32" s="18"/>
+      <c r="C32" s="17"/>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="18"/>
+      <c r="C33" s="17"/>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="18"/>
+      <c r="C34" s="17"/>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="18"/>
+      <c r="C35" s="17"/>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="18"/>
+      <c r="C36" s="17"/>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C37" s="18"/>
+      <c r="C37" s="17"/>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C38" s="18"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C39" s="18"/>
+      <c r="C39" s="17"/>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C40" s="18"/>
+      <c r="C40" s="17"/>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C41" s="18"/>
+      <c r="C41" s="17"/>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C42" s="18"/>
+      <c r="C42" s="17"/>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C43" s="18"/>
+      <c r="C43" s="17"/>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C44" s="18"/>
+      <c r="C44" s="17"/>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C45" s="18"/>
+      <c r="C45" s="17"/>
     </row>
     <row r="46" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C46" s="18"/>
+      <c r="C46" s="17"/>
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C47" s="18"/>
+      <c r="C47" s="17"/>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C48" s="18"/>
+      <c r="C48" s="17"/>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="18"/>
+      <c r="C49" s="17"/>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C50" s="18"/>
+      <c r="C50" s="17"/>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C51" s="18"/>
+      <c r="C51" s="17"/>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C52" s="18"/>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="18"/>
+      <c r="C52" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>

--- a/DISPO.xlsx
+++ b/DISPO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A0BBA7-55C7-4DA2-93DB-5830662AFCFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D3F40E-71B5-46D3-89F2-C884A8DFA384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D5233C47-2897-4F0E-9138-F4B2B2ED9B28}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="104">
   <si>
     <t xml:space="preserve">Z01 - A VISTA </t>
   </si>
@@ -915,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}">
-  <dimension ref="A1:AP52"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
@@ -3019,90 +3019,7 @@
       <c r="AP26" s="4"/>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A27" s="13">
-        <v>4422</v>
-      </c>
-      <c r="B27" s="15">
-        <v>13263499</v>
-      </c>
-      <c r="C27" s="16">
-        <v>5274757</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="13">
-        <v>43263432</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H27" s="6">
-        <v>46147</v>
-      </c>
-      <c r="I27" s="12"/>
-      <c r="J27" s="3">
-        <v>36</v>
-      </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="R27" s="4">
-        <v>1</v>
-      </c>
-      <c r="S27" s="4">
-        <v>3</v>
-      </c>
-      <c r="T27" s="4">
-        <v>2</v>
-      </c>
-      <c r="U27" s="4">
-        <v>3</v>
-      </c>
-      <c r="V27" s="4">
-        <v>2</v>
-      </c>
-      <c r="W27" s="4">
-        <v>1</v>
-      </c>
-      <c r="X27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB27" s="4"/>
-      <c r="AC27" s="4"/>
-      <c r="AD27" s="4"/>
-      <c r="AE27" s="4"/>
-      <c r="AF27" s="4"/>
-      <c r="AG27" s="4"/>
-      <c r="AH27" s="4"/>
-      <c r="AI27" s="4"/>
-      <c r="AJ27" s="4"/>
-      <c r="AK27" s="4"/>
-      <c r="AL27" s="4"/>
-      <c r="AM27" s="4"/>
-      <c r="AN27" s="4"/>
-      <c r="AO27" s="4"/>
-      <c r="AP27" s="4"/>
+      <c r="C27" s="17"/>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="C28" s="17"/>
@@ -3175,9 +3092,6 @@
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C51" s="17"/>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C52" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="B1:AA26" xr:uid="{D63AD4AA-E078-4C28-AB28-3D04A26ABB28}"/>
